--- a/gaa_rankings_pivot.xlsx
+++ b/gaa_rankings_pivot.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL34"/>
+  <dimension ref="A1:AM34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -623,6 +623,11 @@
           <t>2026-02-24</t>
         </is>
       </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -741,6 +746,9 @@
       <c r="AL2" t="n">
         <v>36.56</v>
       </c>
+      <c r="AM2" t="n">
+        <v>38.19</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -859,6 +867,9 @@
       <c r="AL3" t="n">
         <v>60.84</v>
       </c>
+      <c r="AM3" t="n">
+        <v>60.32</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -977,6 +988,9 @@
       <c r="AL4" t="n">
         <v>42.01</v>
       </c>
+      <c r="AM4" t="n">
+        <v>40.68</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1095,6 +1109,9 @@
       <c r="AL5" t="n">
         <v>53.24</v>
       </c>
+      <c r="AM5" t="n">
+        <v>51.74</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1213,6 +1230,9 @@
       <c r="AL6" t="n">
         <v>48.03</v>
       </c>
+      <c r="AM6" t="n">
+        <v>49.72</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1331,6 +1351,9 @@
       <c r="AL7" t="n">
         <v>58.38</v>
       </c>
+      <c r="AM7" t="n">
+        <v>57.25</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1449,6 +1472,9 @@
       <c r="AL8" t="n">
         <v>58.59</v>
       </c>
+      <c r="AM8" t="n">
+        <v>59.72</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1567,6 +1593,9 @@
       <c r="AL9" t="n">
         <v>68.19</v>
       </c>
+      <c r="AM9" t="n">
+        <v>67.44</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1685,6 +1714,9 @@
       <c r="AL10" t="n">
         <v>56.79</v>
       </c>
+      <c r="AM10" t="n">
+        <v>56.84</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1803,6 +1835,9 @@
       <c r="AL11" t="n">
         <v>60.31</v>
       </c>
+      <c r="AM11" t="n">
+        <v>61.59</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1921,6 +1956,9 @@
       <c r="AL12" t="n">
         <v>42.7</v>
       </c>
+      <c r="AM12" t="n">
+        <v>42.65</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2039,6 +2077,9 @@
       <c r="AL13" t="n">
         <v>61.79</v>
       </c>
+      <c r="AM13" t="n">
+        <v>62.54</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2157,6 +2198,9 @@
       <c r="AL14" t="n">
         <v>67.98</v>
       </c>
+      <c r="AM14" t="n">
+        <v>68.08</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2275,6 +2319,9 @@
       <c r="AL15" t="n">
         <v>52.38</v>
       </c>
+      <c r="AM15" t="n">
+        <v>51.82</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2393,6 +2440,9 @@
       <c r="AL16" t="n">
         <v>44.58</v>
       </c>
+      <c r="AM16" t="n">
+        <v>46.46</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2511,6 +2561,9 @@
       <c r="AL17" t="n">
         <v>37.25</v>
       </c>
+      <c r="AM17" t="n">
+        <v>35.77</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2629,6 +2682,9 @@
       <c r="AL18" t="n">
         <v>47.15</v>
       </c>
+      <c r="AM18" t="n">
+        <v>45.46</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2747,6 +2803,9 @@
       <c r="AL19" t="n">
         <v>33.52</v>
       </c>
+      <c r="AM19" t="n">
+        <v>33.97</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2865,6 +2924,9 @@
       <c r="AL20" t="n">
         <v>36.99</v>
       </c>
+      <c r="AM20" t="n">
+        <v>38.32</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2983,6 +3045,9 @@
       <c r="AL21" t="n">
         <v>55.23</v>
       </c>
+      <c r="AM21" t="n">
+        <v>56.73</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -3101,6 +3166,9 @@
       <c r="AL22" t="n">
         <v>63.37</v>
       </c>
+      <c r="AM22" t="n">
+        <v>63.89</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -3219,6 +3287,9 @@
       <c r="AL23" t="n">
         <v>60.78</v>
       </c>
+      <c r="AM23" t="n">
+        <v>61.34</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -3337,6 +3408,9 @@
       <c r="AL24" t="n">
         <v>55.55</v>
       </c>
+      <c r="AM24" t="n">
+        <v>55.45</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -3455,6 +3529,9 @@
       <c r="AL25" t="n">
         <v>36.73</v>
       </c>
+      <c r="AM25" t="n">
+        <v>36.73</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -3573,6 +3650,9 @@
       <c r="AL26" t="n">
         <v>44.92</v>
       </c>
+      <c r="AM26" t="n">
+        <v>44.85</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -3691,6 +3771,9 @@
       <c r="AL27" t="n">
         <v>57.02</v>
       </c>
+      <c r="AM27" t="n">
+        <v>55.74</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -3809,6 +3892,9 @@
       <c r="AL28" t="n">
         <v>46.17</v>
       </c>
+      <c r="AM28" t="n">
+        <v>45.22</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -3927,6 +4013,9 @@
       <c r="AL29" t="n">
         <v>35.36</v>
       </c>
+      <c r="AM29" t="n">
+        <v>36.84</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -4045,6 +4134,9 @@
       <c r="AL30" t="n">
         <v>59.13</v>
       </c>
+      <c r="AM30" t="n">
+        <v>59.2</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -4163,6 +4255,9 @@
       <c r="AL31" t="n">
         <v>30.09</v>
       </c>
+      <c r="AM31" t="n">
+        <v>29.64</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -4281,6 +4376,9 @@
       <c r="AL32" t="n">
         <v>48.83</v>
       </c>
+      <c r="AM32" t="n">
+        <v>46.95</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -4399,6 +4497,9 @@
       <c r="AL33" t="n">
         <v>44.59</v>
       </c>
+      <c r="AM33" t="n">
+        <v>45.54</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -4516,6 +4617,9 @@
       </c>
       <c r="AL34" t="n">
         <v>44.95</v>
+      </c>
+      <c r="AM34" t="n">
+        <v>43.32</v>
       </c>
     </row>
   </sheetData>

--- a/gaa_rankings_pivot.xlsx
+++ b/gaa_rankings_pivot.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM34"/>
+  <dimension ref="A1:AN34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -628,6 +628,11 @@
           <t>2026-03-03</t>
         </is>
       </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -749,6 +754,9 @@
       <c r="AM2" t="n">
         <v>38.19</v>
       </c>
+      <c r="AN2" t="n">
+        <v>38.19</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -870,6 +878,9 @@
       <c r="AM3" t="n">
         <v>60.32</v>
       </c>
+      <c r="AN3" t="n">
+        <v>60.32</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -991,6 +1002,9 @@
       <c r="AM4" t="n">
         <v>40.68</v>
       </c>
+      <c r="AN4" t="n">
+        <v>40.68</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1112,6 +1126,9 @@
       <c r="AM5" t="n">
         <v>51.74</v>
       </c>
+      <c r="AN5" t="n">
+        <v>51.74</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1233,6 +1250,9 @@
       <c r="AM6" t="n">
         <v>49.72</v>
       </c>
+      <c r="AN6" t="n">
+        <v>49.72</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1354,6 +1374,9 @@
       <c r="AM7" t="n">
         <v>57.25</v>
       </c>
+      <c r="AN7" t="n">
+        <v>57.25</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1475,6 +1498,9 @@
       <c r="AM8" t="n">
         <v>59.72</v>
       </c>
+      <c r="AN8" t="n">
+        <v>59.72</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1596,6 +1622,9 @@
       <c r="AM9" t="n">
         <v>67.44</v>
       </c>
+      <c r="AN9" t="n">
+        <v>67.44</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1717,6 +1746,9 @@
       <c r="AM10" t="n">
         <v>56.84</v>
       </c>
+      <c r="AN10" t="n">
+        <v>56.84</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1838,6 +1870,9 @@
       <c r="AM11" t="n">
         <v>61.59</v>
       </c>
+      <c r="AN11" t="n">
+        <v>61.59</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1959,6 +1994,9 @@
       <c r="AM12" t="n">
         <v>42.65</v>
       </c>
+      <c r="AN12" t="n">
+        <v>42.65</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2080,6 +2118,9 @@
       <c r="AM13" t="n">
         <v>62.54</v>
       </c>
+      <c r="AN13" t="n">
+        <v>62.54</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2201,6 +2242,9 @@
       <c r="AM14" t="n">
         <v>68.08</v>
       </c>
+      <c r="AN14" t="n">
+        <v>68.08</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2322,6 +2366,9 @@
       <c r="AM15" t="n">
         <v>51.82</v>
       </c>
+      <c r="AN15" t="n">
+        <v>51.82</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2443,6 +2490,9 @@
       <c r="AM16" t="n">
         <v>46.46</v>
       </c>
+      <c r="AN16" t="n">
+        <v>46.46</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2564,6 +2614,9 @@
       <c r="AM17" t="n">
         <v>35.77</v>
       </c>
+      <c r="AN17" t="n">
+        <v>35.77</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2685,6 +2738,9 @@
       <c r="AM18" t="n">
         <v>45.46</v>
       </c>
+      <c r="AN18" t="n">
+        <v>45.46</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2806,6 +2862,9 @@
       <c r="AM19" t="n">
         <v>33.97</v>
       </c>
+      <c r="AN19" t="n">
+        <v>33.97</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2927,6 +2986,9 @@
       <c r="AM20" t="n">
         <v>38.32</v>
       </c>
+      <c r="AN20" t="n">
+        <v>38.32</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -3048,6 +3110,9 @@
       <c r="AM21" t="n">
         <v>56.73</v>
       </c>
+      <c r="AN21" t="n">
+        <v>56.73</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -3169,6 +3234,9 @@
       <c r="AM22" t="n">
         <v>63.89</v>
       </c>
+      <c r="AN22" t="n">
+        <v>63.89</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -3290,6 +3358,9 @@
       <c r="AM23" t="n">
         <v>61.34</v>
       </c>
+      <c r="AN23" t="n">
+        <v>61.34</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -3411,6 +3482,9 @@
       <c r="AM24" t="n">
         <v>55.45</v>
       </c>
+      <c r="AN24" t="n">
+        <v>55.45</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -3532,6 +3606,9 @@
       <c r="AM25" t="n">
         <v>36.73</v>
       </c>
+      <c r="AN25" t="n">
+        <v>36.73</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -3653,6 +3730,9 @@
       <c r="AM26" t="n">
         <v>44.85</v>
       </c>
+      <c r="AN26" t="n">
+        <v>44.85</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -3774,6 +3854,9 @@
       <c r="AM27" t="n">
         <v>55.74</v>
       </c>
+      <c r="AN27" t="n">
+        <v>55.74</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -3895,6 +3978,9 @@
       <c r="AM28" t="n">
         <v>45.22</v>
       </c>
+      <c r="AN28" t="n">
+        <v>45.22</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -4016,6 +4102,9 @@
       <c r="AM29" t="n">
         <v>36.84</v>
       </c>
+      <c r="AN29" t="n">
+        <v>36.84</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -4137,6 +4226,9 @@
       <c r="AM30" t="n">
         <v>59.2</v>
       </c>
+      <c r="AN30" t="n">
+        <v>59.2</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -4258,6 +4350,9 @@
       <c r="AM31" t="n">
         <v>29.64</v>
       </c>
+      <c r="AN31" t="n">
+        <v>29.64</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -4379,6 +4474,9 @@
       <c r="AM32" t="n">
         <v>46.95</v>
       </c>
+      <c r="AN32" t="n">
+        <v>46.95</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -4500,6 +4598,9 @@
       <c r="AM33" t="n">
         <v>45.54</v>
       </c>
+      <c r="AN33" t="n">
+        <v>45.54</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -4619,6 +4720,9 @@
         <v>44.95</v>
       </c>
       <c r="AM34" t="n">
+        <v>43.32</v>
+      </c>
+      <c r="AN34" t="n">
         <v>43.32</v>
       </c>
     </row>

--- a/gaa_rankings_pivot.xlsx
+++ b/gaa_rankings_pivot.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN34"/>
+  <dimension ref="A1:AO34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -633,6 +633,11 @@
           <t>2026-03-10</t>
         </is>
       </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -757,6 +762,9 @@
       <c r="AN2" t="n">
         <v>38.19</v>
       </c>
+      <c r="AO2" t="n">
+        <v>38.73</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -881,6 +889,9 @@
       <c r="AN3" t="n">
         <v>60.32</v>
       </c>
+      <c r="AO3" t="n">
+        <v>61.68</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1005,6 +1016,9 @@
       <c r="AN4" t="n">
         <v>40.68</v>
       </c>
+      <c r="AO4" t="n">
+        <v>38.92</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1129,6 +1143,9 @@
       <c r="AN5" t="n">
         <v>51.74</v>
       </c>
+      <c r="AO5" t="n">
+        <v>52.23</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1253,6 +1270,9 @@
       <c r="AN6" t="n">
         <v>49.72</v>
       </c>
+      <c r="AO6" t="n">
+        <v>48.11</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1377,6 +1397,9 @@
       <c r="AN7" t="n">
         <v>57.25</v>
       </c>
+      <c r="AO7" t="n">
+        <v>57.71</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1501,6 +1524,9 @@
       <c r="AN8" t="n">
         <v>59.72</v>
       </c>
+      <c r="AO8" t="n">
+        <v>58.61</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1625,6 +1651,9 @@
       <c r="AN9" t="n">
         <v>67.44</v>
       </c>
+      <c r="AO9" t="n">
+        <v>65.63</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1749,6 +1778,9 @@
       <c r="AN10" t="n">
         <v>56.84</v>
       </c>
+      <c r="AO10" t="n">
+        <v>57.14</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1873,6 +1905,9 @@
       <c r="AN11" t="n">
         <v>61.59</v>
       </c>
+      <c r="AO11" t="n">
+        <v>60.23</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1997,6 +2032,9 @@
       <c r="AN12" t="n">
         <v>42.65</v>
       </c>
+      <c r="AO12" t="n">
+        <v>43.86</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2121,6 +2159,9 @@
       <c r="AN13" t="n">
         <v>62.54</v>
       </c>
+      <c r="AO13" t="n">
+        <v>63.01</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2245,6 +2286,9 @@
       <c r="AN14" t="n">
         <v>68.08</v>
       </c>
+      <c r="AO14" t="n">
+        <v>68.66</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2369,6 +2413,9 @@
       <c r="AN15" t="n">
         <v>51.82</v>
       </c>
+      <c r="AO15" t="n">
+        <v>51.36</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2493,6 +2540,9 @@
       <c r="AN16" t="n">
         <v>46.46</v>
       </c>
+      <c r="AO16" t="n">
+        <v>45.25</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2617,6 +2667,9 @@
       <c r="AN17" t="n">
         <v>35.77</v>
       </c>
+      <c r="AO17" t="n">
+        <v>37.36</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2741,6 +2794,9 @@
       <c r="AN18" t="n">
         <v>45.46</v>
       </c>
+      <c r="AO18" t="n">
+        <v>44.53</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2865,6 +2921,9 @@
       <c r="AN19" t="n">
         <v>33.97</v>
       </c>
+      <c r="AO19" t="n">
+        <v>35.73</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2989,6 +3048,9 @@
       <c r="AN20" t="n">
         <v>38.32</v>
       </c>
+      <c r="AO20" t="n">
+        <v>36.73</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -3113,6 +3175,9 @@
       <c r="AN21" t="n">
         <v>56.73</v>
       </c>
+      <c r="AO21" t="n">
+        <v>57.84</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -3237,6 +3302,9 @@
       <c r="AN22" t="n">
         <v>63.89</v>
       </c>
+      <c r="AO22" t="n">
+        <v>63.31</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -3361,6 +3429,9 @@
       <c r="AN23" t="n">
         <v>61.34</v>
       </c>
+      <c r="AO23" t="n">
+        <v>62.1</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -3485,6 +3556,9 @@
       <c r="AN24" t="n">
         <v>55.45</v>
       </c>
+      <c r="AO24" t="n">
+        <v>54.98</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -3609,6 +3683,9 @@
       <c r="AN25" t="n">
         <v>36.73</v>
       </c>
+      <c r="AO25" t="n">
+        <v>36.73</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -3733,6 +3810,9 @@
       <c r="AN26" t="n">
         <v>44.85</v>
       </c>
+      <c r="AO26" t="n">
+        <v>44.36</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -3857,6 +3937,9 @@
       <c r="AN27" t="n">
         <v>55.74</v>
       </c>
+      <c r="AO27" t="n">
+        <v>57.55</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -3981,6 +4064,9 @@
       <c r="AN28" t="n">
         <v>45.22</v>
       </c>
+      <c r="AO28" t="n">
+        <v>44.92</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -4105,6 +4191,9 @@
       <c r="AN29" t="n">
         <v>36.84</v>
       </c>
+      <c r="AO29" t="n">
+        <v>36.47</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -4229,6 +4318,9 @@
       <c r="AN30" t="n">
         <v>59.2</v>
       </c>
+      <c r="AO30" t="n">
+        <v>58.44</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -4353,6 +4445,9 @@
       <c r="AN31" t="n">
         <v>29.64</v>
       </c>
+      <c r="AO31" t="n">
+        <v>29.1</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -4477,6 +4572,9 @@
       <c r="AN32" t="n">
         <v>46.95</v>
       </c>
+      <c r="AO32" t="n">
+        <v>47.88</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -4601,6 +4699,9 @@
       <c r="AN33" t="n">
         <v>45.54</v>
       </c>
+      <c r="AO33" t="n">
+        <v>47.15</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -4724,6 +4825,9 @@
       </c>
       <c r="AN34" t="n">
         <v>43.32</v>
+      </c>
+      <c r="AO34" t="n">
+        <v>43.69</v>
       </c>
     </row>
   </sheetData>

--- a/gaa_rankings_pivot.xlsx
+++ b/gaa_rankings_pivot.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AO34"/>
+  <dimension ref="A1:AP34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -638,6 +638,11 @@
           <t>2026-03-17</t>
         </is>
       </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -765,6 +770,9 @@
       <c r="AO2" t="n">
         <v>38.73</v>
       </c>
+      <c r="AP2" t="n">
+        <v>39.21</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -892,6 +900,9 @@
       <c r="AO3" t="n">
         <v>61.68</v>
       </c>
+      <c r="AP3" t="n">
+        <v>62.2</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1019,6 +1030,9 @@
       <c r="AO4" t="n">
         <v>38.92</v>
       </c>
+      <c r="AP4" t="n">
+        <v>40</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1146,6 +1160,9 @@
       <c r="AO5" t="n">
         <v>52.23</v>
       </c>
+      <c r="AP5" t="n">
+        <v>51.98</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1273,6 +1290,9 @@
       <c r="AO6" t="n">
         <v>48.11</v>
       </c>
+      <c r="AP6" t="n">
+        <v>46.97</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1400,6 +1420,9 @@
       <c r="AO7" t="n">
         <v>57.71</v>
       </c>
+      <c r="AP7" t="n">
+        <v>59.01</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1527,6 +1550,9 @@
       <c r="AO8" t="n">
         <v>58.61</v>
       </c>
+      <c r="AP8" t="n">
+        <v>58.86</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1654,6 +1680,9 @@
       <c r="AO9" t="n">
         <v>65.63</v>
       </c>
+      <c r="AP9" t="n">
+        <v>65.87</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1781,6 +1810,9 @@
       <c r="AO10" t="n">
         <v>57.14</v>
       </c>
+      <c r="AP10" t="n">
+        <v>55.22</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1908,6 +1940,9 @@
       <c r="AO11" t="n">
         <v>60.23</v>
       </c>
+      <c r="AP11" t="n">
+        <v>59.73</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2035,6 +2070,9 @@
       <c r="AO12" t="n">
         <v>43.86</v>
       </c>
+      <c r="AP12" t="n">
+        <v>43.16</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2162,6 +2200,9 @@
       <c r="AO13" t="n">
         <v>63.01</v>
       </c>
+      <c r="AP13" t="n">
+        <v>63.51</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2289,6 +2330,9 @@
       <c r="AO14" t="n">
         <v>68.66</v>
       </c>
+      <c r="AP14" t="n">
+        <v>68.14</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2416,6 +2460,9 @@
       <c r="AO15" t="n">
         <v>51.36</v>
       </c>
+      <c r="AP15" t="n">
+        <v>50.83</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2543,6 +2590,9 @@
       <c r="AO16" t="n">
         <v>45.25</v>
       </c>
+      <c r="AP16" t="n">
+        <v>47.17</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2670,6 +2720,9 @@
       <c r="AO17" t="n">
         <v>37.36</v>
       </c>
+      <c r="AP17" t="n">
+        <v>37.34</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2797,6 +2850,9 @@
       <c r="AO18" t="n">
         <v>44.53</v>
       </c>
+      <c r="AP18" t="n">
+        <v>45.23</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2924,6 +2980,9 @@
       <c r="AO19" t="n">
         <v>35.73</v>
       </c>
+      <c r="AP19" t="n">
+        <v>35.25</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -3051,6 +3110,9 @@
       <c r="AO20" t="n">
         <v>36.73</v>
       </c>
+      <c r="AP20" t="n">
+        <v>37.27</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -3178,6 +3240,9 @@
       <c r="AO21" t="n">
         <v>57.84</v>
       </c>
+      <c r="AP21" t="n">
+        <v>58.37</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -3305,6 +3370,9 @@
       <c r="AO22" t="n">
         <v>63.31</v>
       </c>
+      <c r="AP22" t="n">
+        <v>63.74</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -3432,6 +3500,9 @@
       <c r="AO23" t="n">
         <v>62.1</v>
       </c>
+      <c r="AP23" t="n">
+        <v>62.18</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -3559,6 +3630,9 @@
       <c r="AO24" t="n">
         <v>54.98</v>
       </c>
+      <c r="AP24" t="n">
+        <v>54.74</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -3686,6 +3760,9 @@
       <c r="AO25" t="n">
         <v>36.73</v>
       </c>
+      <c r="AP25" t="n">
+        <v>36.73</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -3813,6 +3890,9 @@
       <c r="AO26" t="n">
         <v>44.36</v>
       </c>
+      <c r="AP26" t="n">
+        <v>44.28</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -3940,6 +4020,9 @@
       <c r="AO27" t="n">
         <v>57.55</v>
       </c>
+      <c r="AP27" t="n">
+        <v>57.12</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -4067,6 +4150,9 @@
       <c r="AO28" t="n">
         <v>44.92</v>
       </c>
+      <c r="AP28" t="n">
+        <v>46.06</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -4194,6 +4280,9 @@
       <c r="AO29" t="n">
         <v>36.47</v>
       </c>
+      <c r="AP29" t="n">
+        <v>36.78</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -4321,6 +4410,9 @@
       <c r="AO30" t="n">
         <v>58.44</v>
       </c>
+      <c r="AP30" t="n">
+        <v>57.14</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -4448,6 +4540,9 @@
       <c r="AO31" t="n">
         <v>29.1</v>
       </c>
+      <c r="AP31" t="n">
+        <v>28.79</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -4575,6 +4670,9 @@
       <c r="AO32" t="n">
         <v>47.88</v>
       </c>
+      <c r="AP32" t="n">
+        <v>47.03</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -4702,6 +4800,9 @@
       <c r="AO33" t="n">
         <v>47.15</v>
       </c>
+      <c r="AP33" t="n">
+        <v>48</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -4828,6 +4929,9 @@
       </c>
       <c r="AO34" t="n">
         <v>43.69</v>
+      </c>
+      <c r="AP34" t="n">
+        <v>42.09</v>
       </c>
     </row>
   </sheetData>

--- a/gaa_rankings_pivot.xlsx
+++ b/gaa_rankings_pivot.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AP34"/>
+  <dimension ref="A1:AQ34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -643,6 +643,11 @@
           <t>2026-03-24</t>
         </is>
       </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -773,6 +778,9 @@
       <c r="AP2" t="n">
         <v>39.21</v>
       </c>
+      <c r="AQ2" t="n">
+        <v>39.21</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -903,6 +911,9 @@
       <c r="AP3" t="n">
         <v>62.2</v>
       </c>
+      <c r="AQ3" t="n">
+        <v>62.2</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1033,6 +1044,9 @@
       <c r="AP4" t="n">
         <v>40</v>
       </c>
+      <c r="AQ4" t="n">
+        <v>40.7</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1163,6 +1177,9 @@
       <c r="AP5" t="n">
         <v>51.98</v>
       </c>
+      <c r="AQ5" t="n">
+        <v>51.98</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1293,6 +1310,9 @@
       <c r="AP6" t="n">
         <v>46.97</v>
       </c>
+      <c r="AQ6" t="n">
+        <v>46.97</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1423,6 +1443,9 @@
       <c r="AP7" t="n">
         <v>59.01</v>
       </c>
+      <c r="AQ7" t="n">
+        <v>58.36</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1553,6 +1576,9 @@
       <c r="AP8" t="n">
         <v>58.86</v>
       </c>
+      <c r="AQ8" t="n">
+        <v>58.86</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1683,6 +1709,9 @@
       <c r="AP9" t="n">
         <v>65.87</v>
       </c>
+      <c r="AQ9" t="n">
+        <v>66.97</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1813,6 +1842,9 @@
       <c r="AP10" t="n">
         <v>55.22</v>
       </c>
+      <c r="AQ10" t="n">
+        <v>55.54</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1943,6 +1975,9 @@
       <c r="AP11" t="n">
         <v>59.73</v>
       </c>
+      <c r="AQ11" t="n">
+        <v>59.73</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2073,6 +2108,9 @@
       <c r="AP12" t="n">
         <v>43.16</v>
       </c>
+      <c r="AQ12" t="n">
+        <v>43.16</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2203,6 +2241,9 @@
       <c r="AP13" t="n">
         <v>63.51</v>
       </c>
+      <c r="AQ13" t="n">
+        <v>63.51</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2333,6 +2374,9 @@
       <c r="AP14" t="n">
         <v>68.14</v>
       </c>
+      <c r="AQ14" t="n">
+        <v>67.04000000000001</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2463,6 +2507,9 @@
       <c r="AP15" t="n">
         <v>50.83</v>
       </c>
+      <c r="AQ15" t="n">
+        <v>50.83</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2593,6 +2640,9 @@
       <c r="AP16" t="n">
         <v>47.17</v>
       </c>
+      <c r="AQ16" t="n">
+        <v>47.17</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2723,6 +2773,9 @@
       <c r="AP17" t="n">
         <v>37.34</v>
       </c>
+      <c r="AQ17" t="n">
+        <v>37.34</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2853,6 +2906,9 @@
       <c r="AP18" t="n">
         <v>45.23</v>
       </c>
+      <c r="AQ18" t="n">
+        <v>45.23</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2983,6 +3039,9 @@
       <c r="AP19" t="n">
         <v>35.25</v>
       </c>
+      <c r="AQ19" t="n">
+        <v>35.25</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -3113,6 +3172,9 @@
       <c r="AP20" t="n">
         <v>37.27</v>
       </c>
+      <c r="AQ20" t="n">
+        <v>36.57</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -3243,6 +3305,9 @@
       <c r="AP21" t="n">
         <v>58.37</v>
       </c>
+      <c r="AQ21" t="n">
+        <v>58.37</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -3373,6 +3438,9 @@
       <c r="AP22" t="n">
         <v>63.74</v>
       </c>
+      <c r="AQ22" t="n">
+        <v>63.74</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -3503,6 +3571,9 @@
       <c r="AP23" t="n">
         <v>62.18</v>
       </c>
+      <c r="AQ23" t="n">
+        <v>62.83</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -3633,6 +3704,9 @@
       <c r="AP24" t="n">
         <v>54.74</v>
       </c>
+      <c r="AQ24" t="n">
+        <v>54.74</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -3763,6 +3837,9 @@
       <c r="AP25" t="n">
         <v>36.73</v>
       </c>
+      <c r="AQ25" t="n">
+        <v>36.73</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -3893,6 +3970,9 @@
       <c r="AP26" t="n">
         <v>44.28</v>
       </c>
+      <c r="AQ26" t="n">
+        <v>44.28</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -4023,6 +4103,9 @@
       <c r="AP27" t="n">
         <v>57.12</v>
       </c>
+      <c r="AQ27" t="n">
+        <v>57.12</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -4153,6 +4236,9 @@
       <c r="AP28" t="n">
         <v>46.06</v>
       </c>
+      <c r="AQ28" t="n">
+        <v>46.06</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -4283,6 +4369,9 @@
       <c r="AP29" t="n">
         <v>36.78</v>
       </c>
+      <c r="AQ29" t="n">
+        <v>36.78</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -4413,6 +4502,9 @@
       <c r="AP30" t="n">
         <v>57.14</v>
       </c>
+      <c r="AQ30" t="n">
+        <v>57.14</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -4543,6 +4635,9 @@
       <c r="AP31" t="n">
         <v>28.79</v>
       </c>
+      <c r="AQ31" t="n">
+        <v>28.79</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -4673,6 +4768,9 @@
       <c r="AP32" t="n">
         <v>47.03</v>
       </c>
+      <c r="AQ32" t="n">
+        <v>47.03</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -4803,6 +4901,9 @@
       <c r="AP33" t="n">
         <v>48</v>
       </c>
+      <c r="AQ33" t="n">
+        <v>47.68</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -4931,6 +5032,9 @@
         <v>43.69</v>
       </c>
       <c r="AP34" t="n">
+        <v>42.09</v>
+      </c>
+      <c r="AQ34" t="n">
         <v>42.09</v>
       </c>
     </row>

--- a/gaa_rankings_pivot.xlsx
+++ b/gaa_rankings_pivot.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AQ34"/>
+  <dimension ref="A1:AR34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -648,6 +648,11 @@
           <t>2026-03-31</t>
         </is>
       </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -781,6 +786,9 @@
       <c r="AQ2" t="n">
         <v>39.21</v>
       </c>
+      <c r="AR2" t="n">
+        <v>39.21</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -914,6 +922,9 @@
       <c r="AQ3" t="n">
         <v>62.2</v>
       </c>
+      <c r="AR3" t="n">
+        <v>62.2</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1047,6 +1058,9 @@
       <c r="AQ4" t="n">
         <v>40.7</v>
       </c>
+      <c r="AR4" t="n">
+        <v>40.7</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1180,6 +1194,9 @@
       <c r="AQ5" t="n">
         <v>51.98</v>
       </c>
+      <c r="AR5" t="n">
+        <v>51.98</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1313,6 +1330,9 @@
       <c r="AQ6" t="n">
         <v>46.97</v>
       </c>
+      <c r="AR6" t="n">
+        <v>46.97</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1446,6 +1466,9 @@
       <c r="AQ7" t="n">
         <v>58.36</v>
       </c>
+      <c r="AR7" t="n">
+        <v>58.36</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1579,6 +1602,9 @@
       <c r="AQ8" t="n">
         <v>58.86</v>
       </c>
+      <c r="AR8" t="n">
+        <v>58.86</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1712,6 +1738,9 @@
       <c r="AQ9" t="n">
         <v>66.97</v>
       </c>
+      <c r="AR9" t="n">
+        <v>66.97</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1845,6 +1874,9 @@
       <c r="AQ10" t="n">
         <v>55.54</v>
       </c>
+      <c r="AR10" t="n">
+        <v>55.54</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1978,6 +2010,9 @@
       <c r="AQ11" t="n">
         <v>59.73</v>
       </c>
+      <c r="AR11" t="n">
+        <v>59.73</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2111,6 +2146,9 @@
       <c r="AQ12" t="n">
         <v>43.16</v>
       </c>
+      <c r="AR12" t="n">
+        <v>43.16</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2244,6 +2282,9 @@
       <c r="AQ13" t="n">
         <v>63.51</v>
       </c>
+      <c r="AR13" t="n">
+        <v>63.51</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2377,6 +2418,9 @@
       <c r="AQ14" t="n">
         <v>67.04000000000001</v>
       </c>
+      <c r="AR14" t="n">
+        <v>67.04000000000001</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2510,6 +2554,9 @@
       <c r="AQ15" t="n">
         <v>50.83</v>
       </c>
+      <c r="AR15" t="n">
+        <v>50.83</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2643,6 +2690,9 @@
       <c r="AQ16" t="n">
         <v>47.17</v>
       </c>
+      <c r="AR16" t="n">
+        <v>47.17</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2776,6 +2826,9 @@
       <c r="AQ17" t="n">
         <v>37.34</v>
       </c>
+      <c r="AR17" t="n">
+        <v>37.34</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2909,6 +2962,9 @@
       <c r="AQ18" t="n">
         <v>45.23</v>
       </c>
+      <c r="AR18" t="n">
+        <v>45.23</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -3042,6 +3098,9 @@
       <c r="AQ19" t="n">
         <v>35.25</v>
       </c>
+      <c r="AR19" t="n">
+        <v>35.25</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -3175,6 +3234,9 @@
       <c r="AQ20" t="n">
         <v>36.57</v>
       </c>
+      <c r="AR20" t="n">
+        <v>36.57</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -3308,6 +3370,9 @@
       <c r="AQ21" t="n">
         <v>58.37</v>
       </c>
+      <c r="AR21" t="n">
+        <v>58.37</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -3441,6 +3506,9 @@
       <c r="AQ22" t="n">
         <v>63.74</v>
       </c>
+      <c r="AR22" t="n">
+        <v>63.74</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -3574,6 +3642,9 @@
       <c r="AQ23" t="n">
         <v>62.83</v>
       </c>
+      <c r="AR23" t="n">
+        <v>62.83</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -3707,6 +3778,9 @@
       <c r="AQ24" t="n">
         <v>54.74</v>
       </c>
+      <c r="AR24" t="n">
+        <v>54.74</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -3840,6 +3914,9 @@
       <c r="AQ25" t="n">
         <v>36.73</v>
       </c>
+      <c r="AR25" t="n">
+        <v>36.73</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -3973,6 +4050,9 @@
       <c r="AQ26" t="n">
         <v>44.28</v>
       </c>
+      <c r="AR26" t="n">
+        <v>44.28</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -4106,6 +4186,9 @@
       <c r="AQ27" t="n">
         <v>57.12</v>
       </c>
+      <c r="AR27" t="n">
+        <v>57.12</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -4239,6 +4322,9 @@
       <c r="AQ28" t="n">
         <v>46.06</v>
       </c>
+      <c r="AR28" t="n">
+        <v>46.06</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -4372,6 +4458,9 @@
       <c r="AQ29" t="n">
         <v>36.78</v>
       </c>
+      <c r="AR29" t="n">
+        <v>36.78</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -4505,6 +4594,9 @@
       <c r="AQ30" t="n">
         <v>57.14</v>
       </c>
+      <c r="AR30" t="n">
+        <v>57.14</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -4638,6 +4730,9 @@
       <c r="AQ31" t="n">
         <v>28.79</v>
       </c>
+      <c r="AR31" t="n">
+        <v>28.79</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -4771,6 +4866,9 @@
       <c r="AQ32" t="n">
         <v>47.03</v>
       </c>
+      <c r="AR32" t="n">
+        <v>47.03</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -4904,6 +5002,9 @@
       <c r="AQ33" t="n">
         <v>47.68</v>
       </c>
+      <c r="AR33" t="n">
+        <v>47.68</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -5035,6 +5136,9 @@
         <v>42.09</v>
       </c>
       <c r="AQ34" t="n">
+        <v>42.09</v>
+      </c>
+      <c r="AR34" t="n">
         <v>42.09</v>
       </c>
     </row>

--- a/gaa_rankings_pivot.xlsx
+++ b/gaa_rankings_pivot.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AR34"/>
+  <dimension ref="A1:AS34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -653,6 +653,11 @@
           <t>2026-04-07</t>
         </is>
       </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -789,6 +794,9 @@
       <c r="AR2" t="n">
         <v>39.21</v>
       </c>
+      <c r="AS2" t="n">
+        <v>39.21</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -925,6 +933,9 @@
       <c r="AR3" t="n">
         <v>62.2</v>
       </c>
+      <c r="AS3" t="n">
+        <v>62.69</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1061,6 +1072,9 @@
       <c r="AR4" t="n">
         <v>40.7</v>
       </c>
+      <c r="AS4" t="n">
+        <v>38.29</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1197,6 +1211,9 @@
       <c r="AR5" t="n">
         <v>51.98</v>
       </c>
+      <c r="AS5" t="n">
+        <v>51.98</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1333,6 +1350,9 @@
       <c r="AR6" t="n">
         <v>46.97</v>
       </c>
+      <c r="AS6" t="n">
+        <v>46.97</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1469,6 +1489,9 @@
       <c r="AR7" t="n">
         <v>58.36</v>
       </c>
+      <c r="AS7" t="n">
+        <v>58.49</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1605,6 +1628,9 @@
       <c r="AR8" t="n">
         <v>58.86</v>
       </c>
+      <c r="AS8" t="n">
+        <v>58.86</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1741,6 +1767,9 @@
       <c r="AR9" t="n">
         <v>66.97</v>
       </c>
+      <c r="AS9" t="n">
+        <v>66.97</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1877,6 +1906,9 @@
       <c r="AR10" t="n">
         <v>55.54</v>
       </c>
+      <c r="AS10" t="n">
+        <v>55.54</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2013,6 +2045,9 @@
       <c r="AR11" t="n">
         <v>59.73</v>
       </c>
+      <c r="AS11" t="n">
+        <v>59.73</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2149,6 +2184,9 @@
       <c r="AR12" t="n">
         <v>43.16</v>
       </c>
+      <c r="AS12" t="n">
+        <v>43.16</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2285,6 +2323,9 @@
       <c r="AR13" t="n">
         <v>63.51</v>
       </c>
+      <c r="AS13" t="n">
+        <v>63.51</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2421,6 +2462,9 @@
       <c r="AR14" t="n">
         <v>67.04000000000001</v>
       </c>
+      <c r="AS14" t="n">
+        <v>67.04000000000001</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2557,6 +2601,9 @@
       <c r="AR15" t="n">
         <v>50.83</v>
       </c>
+      <c r="AS15" t="n">
+        <v>50.83</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2693,6 +2740,9 @@
       <c r="AR16" t="n">
         <v>47.17</v>
       </c>
+      <c r="AS16" t="n">
+        <v>49.19</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2829,6 +2879,9 @@
       <c r="AR17" t="n">
         <v>37.34</v>
       </c>
+      <c r="AS17" t="n">
+        <v>40.11</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2965,6 +3018,9 @@
       <c r="AR18" t="n">
         <v>45.23</v>
       </c>
+      <c r="AS18" t="n">
+        <v>45.1</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -3101,6 +3157,9 @@
       <c r="AR19" t="n">
         <v>35.25</v>
       </c>
+      <c r="AS19" t="n">
+        <v>35.24</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -3237,6 +3296,9 @@
       <c r="AR20" t="n">
         <v>36.57</v>
       </c>
+      <c r="AS20" t="n">
+        <v>36.01</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -3373,6 +3435,9 @@
       <c r="AR21" t="n">
         <v>58.37</v>
       </c>
+      <c r="AS21" t="n">
+        <v>58.37</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -3509,6 +3574,9 @@
       <c r="AR22" t="n">
         <v>63.74</v>
       </c>
+      <c r="AS22" t="n">
+        <v>63.75</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -3645,6 +3713,9 @@
       <c r="AR23" t="n">
         <v>62.83</v>
       </c>
+      <c r="AS23" t="n">
+        <v>62.83</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -3781,6 +3852,9 @@
       <c r="AR24" t="n">
         <v>54.74</v>
       </c>
+      <c r="AS24" t="n">
+        <v>54.74</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -3917,6 +3991,9 @@
       <c r="AR25" t="n">
         <v>36.73</v>
       </c>
+      <c r="AS25" t="n">
+        <v>36.67</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -4053,6 +4130,9 @@
       <c r="AR26" t="n">
         <v>44.28</v>
       </c>
+      <c r="AS26" t="n">
+        <v>42.26</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -4189,6 +4269,9 @@
       <c r="AR27" t="n">
         <v>57.12</v>
       </c>
+      <c r="AS27" t="n">
+        <v>57.18</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -4325,6 +4408,9 @@
       <c r="AR28" t="n">
         <v>46.06</v>
       </c>
+      <c r="AS28" t="n">
+        <v>43.29</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -4461,6 +4547,9 @@
       <c r="AR29" t="n">
         <v>36.78</v>
       </c>
+      <c r="AS29" t="n">
+        <v>37.38</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -4597,6 +4686,9 @@
       <c r="AR30" t="n">
         <v>57.14</v>
       </c>
+      <c r="AS30" t="n">
+        <v>56.65</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -4733,6 +4825,9 @@
       <c r="AR31" t="n">
         <v>28.79</v>
       </c>
+      <c r="AS31" t="n">
+        <v>28.19</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -4869,6 +4964,9 @@
       <c r="AR32" t="n">
         <v>47.03</v>
       </c>
+      <c r="AS32" t="n">
+        <v>47.59</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -5005,6 +5103,9 @@
       <c r="AR33" t="n">
         <v>47.68</v>
       </c>
+      <c r="AS33" t="n">
+        <v>47.68</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -5140,6 +5241,9 @@
       </c>
       <c r="AR34" t="n">
         <v>42.09</v>
+      </c>
+      <c r="AS34" t="n">
+        <v>44.5</v>
       </c>
     </row>
   </sheetData>

--- a/gaa_rankings_pivot.xlsx
+++ b/gaa_rankings_pivot.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AS34"/>
+  <dimension ref="A1:AT34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -658,6 +658,11 @@
           <t>2026-04-13</t>
         </is>
       </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -797,6 +802,9 @@
       <c r="AS2" t="n">
         <v>39.21</v>
       </c>
+      <c r="AT2" t="n">
+        <v>39.21</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -936,6 +944,9 @@
       <c r="AS3" t="n">
         <v>62.69</v>
       </c>
+      <c r="AT3" t="n">
+        <v>62.69</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1075,6 +1086,9 @@
       <c r="AS4" t="n">
         <v>38.29</v>
       </c>
+      <c r="AT4" t="n">
+        <v>38.29</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1214,6 +1228,9 @@
       <c r="AS5" t="n">
         <v>51.98</v>
       </c>
+      <c r="AT5" t="n">
+        <v>51.98</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1353,6 +1370,9 @@
       <c r="AS6" t="n">
         <v>46.97</v>
       </c>
+      <c r="AT6" t="n">
+        <v>46.97</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1492,6 +1512,9 @@
       <c r="AS7" t="n">
         <v>58.49</v>
       </c>
+      <c r="AT7" t="n">
+        <v>58.49</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1631,6 +1654,9 @@
       <c r="AS8" t="n">
         <v>58.86</v>
       </c>
+      <c r="AT8" t="n">
+        <v>58.86</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1770,6 +1796,9 @@
       <c r="AS9" t="n">
         <v>66.97</v>
       </c>
+      <c r="AT9" t="n">
+        <v>66.97</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1909,6 +1938,9 @@
       <c r="AS10" t="n">
         <v>55.54</v>
       </c>
+      <c r="AT10" t="n">
+        <v>55.54</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2048,6 +2080,9 @@
       <c r="AS11" t="n">
         <v>59.73</v>
       </c>
+      <c r="AT11" t="n">
+        <v>59.73</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2187,6 +2222,9 @@
       <c r="AS12" t="n">
         <v>43.16</v>
       </c>
+      <c r="AT12" t="n">
+        <v>43.16</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2326,6 +2364,9 @@
       <c r="AS13" t="n">
         <v>63.51</v>
       </c>
+      <c r="AT13" t="n">
+        <v>63.51</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2465,6 +2506,9 @@
       <c r="AS14" t="n">
         <v>67.04000000000001</v>
       </c>
+      <c r="AT14" t="n">
+        <v>67.04000000000001</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2604,6 +2648,9 @@
       <c r="AS15" t="n">
         <v>50.83</v>
       </c>
+      <c r="AT15" t="n">
+        <v>50.83</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2743,6 +2790,9 @@
       <c r="AS16" t="n">
         <v>49.19</v>
       </c>
+      <c r="AT16" t="n">
+        <v>49.19</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2882,6 +2932,9 @@
       <c r="AS17" t="n">
         <v>40.11</v>
       </c>
+      <c r="AT17" t="n">
+        <v>40.11</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -3021,6 +3074,9 @@
       <c r="AS18" t="n">
         <v>45.1</v>
       </c>
+      <c r="AT18" t="n">
+        <v>45.1</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -3160,6 +3216,9 @@
       <c r="AS19" t="n">
         <v>35.24</v>
       </c>
+      <c r="AT19" t="n">
+        <v>35.24</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -3299,6 +3358,9 @@
       <c r="AS20" t="n">
         <v>36.01</v>
       </c>
+      <c r="AT20" t="n">
+        <v>36.01</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -3438,6 +3500,9 @@
       <c r="AS21" t="n">
         <v>58.37</v>
       </c>
+      <c r="AT21" t="n">
+        <v>58.37</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -3577,6 +3642,9 @@
       <c r="AS22" t="n">
         <v>63.75</v>
       </c>
+      <c r="AT22" t="n">
+        <v>63.75</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -3716,6 +3784,9 @@
       <c r="AS23" t="n">
         <v>62.83</v>
       </c>
+      <c r="AT23" t="n">
+        <v>62.83</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -3855,6 +3926,9 @@
       <c r="AS24" t="n">
         <v>54.74</v>
       </c>
+      <c r="AT24" t="n">
+        <v>54.74</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -3994,6 +4068,9 @@
       <c r="AS25" t="n">
         <v>36.67</v>
       </c>
+      <c r="AT25" t="n">
+        <v>36.67</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -4133,6 +4210,9 @@
       <c r="AS26" t="n">
         <v>42.26</v>
       </c>
+      <c r="AT26" t="n">
+        <v>42.26</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -4272,6 +4352,9 @@
       <c r="AS27" t="n">
         <v>57.18</v>
       </c>
+      <c r="AT27" t="n">
+        <v>57.18</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -4411,6 +4494,9 @@
       <c r="AS28" t="n">
         <v>43.29</v>
       </c>
+      <c r="AT28" t="n">
+        <v>43.29</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -4550,6 +4636,9 @@
       <c r="AS29" t="n">
         <v>37.38</v>
       </c>
+      <c r="AT29" t="n">
+        <v>37.38</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -4689,6 +4778,9 @@
       <c r="AS30" t="n">
         <v>56.65</v>
       </c>
+      <c r="AT30" t="n">
+        <v>56.65</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -4828,6 +4920,9 @@
       <c r="AS31" t="n">
         <v>28.19</v>
       </c>
+      <c r="AT31" t="n">
+        <v>28.19</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -4967,6 +5062,9 @@
       <c r="AS32" t="n">
         <v>47.59</v>
       </c>
+      <c r="AT32" t="n">
+        <v>47.59</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -5106,6 +5204,9 @@
       <c r="AS33" t="n">
         <v>47.68</v>
       </c>
+      <c r="AT33" t="n">
+        <v>47.68</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -5243,6 +5344,9 @@
         <v>42.09</v>
       </c>
       <c r="AS34" t="n">
+        <v>44.5</v>
+      </c>
+      <c r="AT34" t="n">
         <v>44.5</v>
       </c>
     </row>

--- a/gaa_rankings_pivot.xlsx
+++ b/gaa_rankings_pivot.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AT34"/>
+  <dimension ref="A1:AU34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -663,6 +663,11 @@
           <t>2026-04-14</t>
         </is>
       </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -805,6 +810,9 @@
       <c r="AT2" t="n">
         <v>39.21</v>
       </c>
+      <c r="AU2" t="n">
+        <v>39.18</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -947,6 +955,9 @@
       <c r="AT3" t="n">
         <v>62.69</v>
       </c>
+      <c r="AU3" t="n">
+        <v>62.69</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1089,6 +1100,9 @@
       <c r="AT4" t="n">
         <v>38.29</v>
       </c>
+      <c r="AU4" t="n">
+        <v>38.29</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1231,6 +1245,9 @@
       <c r="AT5" t="n">
         <v>51.98</v>
       </c>
+      <c r="AU5" t="n">
+        <v>51.23</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1373,6 +1390,9 @@
       <c r="AT6" t="n">
         <v>46.97</v>
       </c>
+      <c r="AU6" t="n">
+        <v>46.97</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1515,6 +1535,9 @@
       <c r="AT7" t="n">
         <v>58.49</v>
       </c>
+      <c r="AU7" t="n">
+        <v>58.49</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1657,6 +1680,9 @@
       <c r="AT8" t="n">
         <v>58.86</v>
       </c>
+      <c r="AU8" t="n">
+        <v>58.89</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1799,6 +1825,9 @@
       <c r="AT9" t="n">
         <v>66.97</v>
       </c>
+      <c r="AU9" t="n">
+        <v>66.97</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1941,6 +1970,9 @@
       <c r="AT10" t="n">
         <v>55.54</v>
       </c>
+      <c r="AU10" t="n">
+        <v>55.54</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2083,6 +2115,9 @@
       <c r="AT11" t="n">
         <v>59.73</v>
       </c>
+      <c r="AU11" t="n">
+        <v>59.87</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2225,6 +2260,9 @@
       <c r="AT12" t="n">
         <v>43.16</v>
       </c>
+      <c r="AU12" t="n">
+        <v>43.16</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2367,6 +2405,9 @@
       <c r="AT13" t="n">
         <v>63.51</v>
       </c>
+      <c r="AU13" t="n">
+        <v>63.51</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2509,6 +2550,9 @@
       <c r="AT14" t="n">
         <v>67.04000000000001</v>
       </c>
+      <c r="AU14" t="n">
+        <v>67.04000000000001</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2651,6 +2695,9 @@
       <c r="AT15" t="n">
         <v>50.83</v>
       </c>
+      <c r="AU15" t="n">
+        <v>51.74</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2793,6 +2840,9 @@
       <c r="AT16" t="n">
         <v>49.19</v>
       </c>
+      <c r="AU16" t="n">
+        <v>48.28</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2935,6 +2985,9 @@
       <c r="AT17" t="n">
         <v>40.11</v>
       </c>
+      <c r="AU17" t="n">
+        <v>40.11</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -3077,6 +3130,9 @@
       <c r="AT18" t="n">
         <v>45.1</v>
       </c>
+      <c r="AU18" t="n">
+        <v>45.1</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -3219,6 +3275,9 @@
       <c r="AT19" t="n">
         <v>35.24</v>
       </c>
+      <c r="AU19" t="n">
+        <v>35.24</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -3361,6 +3420,9 @@
       <c r="AT20" t="n">
         <v>36.01</v>
       </c>
+      <c r="AU20" t="n">
+        <v>36.01</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -3503,6 +3565,9 @@
       <c r="AT21" t="n">
         <v>58.37</v>
       </c>
+      <c r="AU21" t="n">
+        <v>58.72</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -3645,6 +3710,9 @@
       <c r="AT22" t="n">
         <v>63.75</v>
       </c>
+      <c r="AU22" t="n">
+        <v>63.75</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -3787,6 +3855,9 @@
       <c r="AT23" t="n">
         <v>62.83</v>
       </c>
+      <c r="AU23" t="n">
+        <v>59.92</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -3929,6 +4000,9 @@
       <c r="AT24" t="n">
         <v>54.74</v>
       </c>
+      <c r="AU24" t="n">
+        <v>55.49</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -4071,6 +4145,9 @@
       <c r="AT25" t="n">
         <v>36.67</v>
       </c>
+      <c r="AU25" t="n">
+        <v>36.67</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -4213,6 +4290,9 @@
       <c r="AT26" t="n">
         <v>42.26</v>
       </c>
+      <c r="AU26" t="n">
+        <v>42.26</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -4355,6 +4435,9 @@
       <c r="AT27" t="n">
         <v>57.18</v>
       </c>
+      <c r="AU27" t="n">
+        <v>57.18</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -4497,6 +4580,9 @@
       <c r="AT28" t="n">
         <v>43.29</v>
       </c>
+      <c r="AU28" t="n">
+        <v>43.29</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -4639,6 +4725,9 @@
       <c r="AT29" t="n">
         <v>37.38</v>
       </c>
+      <c r="AU29" t="n">
+        <v>37.38</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -4781,6 +4870,9 @@
       <c r="AT30" t="n">
         <v>56.65</v>
       </c>
+      <c r="AU30" t="n">
+        <v>56.65</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -4923,6 +5015,9 @@
       <c r="AT31" t="n">
         <v>28.19</v>
       </c>
+      <c r="AU31" t="n">
+        <v>28.19</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -5065,6 +5160,9 @@
       <c r="AT32" t="n">
         <v>47.59</v>
       </c>
+      <c r="AU32" t="n">
+        <v>50.5</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -5207,6 +5305,9 @@
       <c r="AT33" t="n">
         <v>47.68</v>
       </c>
+      <c r="AU33" t="n">
+        <v>47.33</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -5348,6 +5449,9 @@
       </c>
       <c r="AT34" t="n">
         <v>44.5</v>
+      </c>
+      <c r="AU34" t="n">
+        <v>44.36</v>
       </c>
     </row>
   </sheetData>

--- a/gaa_rankings_pivot.xlsx
+++ b/gaa_rankings_pivot.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AU34"/>
+  <dimension ref="A1:AV34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -668,6 +668,11 @@
           <t>2026-04-21</t>
         </is>
       </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -813,6 +818,9 @@
       <c r="AU2" t="n">
         <v>39.18</v>
       </c>
+      <c r="AV2" t="n">
+        <v>39.18</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -958,6 +966,9 @@
       <c r="AU3" t="n">
         <v>62.69</v>
       </c>
+      <c r="AV3" t="n">
+        <v>62.77</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1103,6 +1114,9 @@
       <c r="AU4" t="n">
         <v>38.29</v>
       </c>
+      <c r="AV4" t="n">
+        <v>38.29</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1248,6 +1262,9 @@
       <c r="AU5" t="n">
         <v>51.23</v>
       </c>
+      <c r="AV5" t="n">
+        <v>51.23</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1393,6 +1410,9 @@
       <c r="AU6" t="n">
         <v>46.97</v>
       </c>
+      <c r="AV6" t="n">
+        <v>46.92</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1538,6 +1558,9 @@
       <c r="AU7" t="n">
         <v>58.49</v>
       </c>
+      <c r="AV7" t="n">
+        <v>58.54</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1683,6 +1706,9 @@
       <c r="AU8" t="n">
         <v>58.89</v>
       </c>
+      <c r="AV8" t="n">
+        <v>58.89</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1828,6 +1854,9 @@
       <c r="AU9" t="n">
         <v>66.97</v>
       </c>
+      <c r="AV9" t="n">
+        <v>64.09999999999999</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1973,6 +2002,9 @@
       <c r="AU10" t="n">
         <v>55.54</v>
       </c>
+      <c r="AV10" t="n">
+        <v>58.41</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2118,6 +2150,9 @@
       <c r="AU11" t="n">
         <v>59.87</v>
       </c>
+      <c r="AV11" t="n">
+        <v>59.87</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2263,6 +2298,9 @@
       <c r="AU12" t="n">
         <v>43.16</v>
       </c>
+      <c r="AV12" t="n">
+        <v>43.08</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2408,6 +2446,9 @@
       <c r="AU13" t="n">
         <v>63.51</v>
       </c>
+      <c r="AV13" t="n">
+        <v>63.53</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2553,6 +2594,9 @@
       <c r="AU14" t="n">
         <v>67.04000000000001</v>
       </c>
+      <c r="AV14" t="n">
+        <v>67.09</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2698,6 +2742,9 @@
       <c r="AU15" t="n">
         <v>51.74</v>
       </c>
+      <c r="AV15" t="n">
+        <v>51.74</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2843,6 +2890,9 @@
       <c r="AU16" t="n">
         <v>48.28</v>
       </c>
+      <c r="AV16" t="n">
+        <v>48.28</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2988,6 +3038,9 @@
       <c r="AU17" t="n">
         <v>40.11</v>
       </c>
+      <c r="AV17" t="n">
+        <v>40.09</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -3133,6 +3186,9 @@
       <c r="AU18" t="n">
         <v>45.1</v>
       </c>
+      <c r="AV18" t="n">
+        <v>45.1</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -3278,6 +3334,9 @@
       <c r="AU19" t="n">
         <v>35.24</v>
       </c>
+      <c r="AV19" t="n">
+        <v>35.24</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -3423,6 +3482,9 @@
       <c r="AU20" t="n">
         <v>36.01</v>
       </c>
+      <c r="AV20" t="n">
+        <v>36.01</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -3568,6 +3630,9 @@
       <c r="AU21" t="n">
         <v>58.72</v>
       </c>
+      <c r="AV21" t="n">
+        <v>58.72</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -3713,6 +3778,9 @@
       <c r="AU22" t="n">
         <v>63.75</v>
       </c>
+      <c r="AV22" t="n">
+        <v>59.8</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -3858,6 +3926,9 @@
       <c r="AU23" t="n">
         <v>59.92</v>
       </c>
+      <c r="AV23" t="n">
+        <v>59.92</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -4003,6 +4074,9 @@
       <c r="AU24" t="n">
         <v>55.49</v>
       </c>
+      <c r="AV24" t="n">
+        <v>55.49</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -4148,6 +4222,9 @@
       <c r="AU25" t="n">
         <v>36.67</v>
       </c>
+      <c r="AV25" t="n">
+        <v>36.67</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -4293,6 +4370,9 @@
       <c r="AU26" t="n">
         <v>42.26</v>
       </c>
+      <c r="AV26" t="n">
+        <v>42.26</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -4438,6 +4518,9 @@
       <c r="AU27" t="n">
         <v>57.18</v>
       </c>
+      <c r="AV27" t="n">
+        <v>61.13</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -4583,6 +4666,9 @@
       <c r="AU28" t="n">
         <v>43.29</v>
       </c>
+      <c r="AV28" t="n">
+        <v>43.29</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -4728,6 +4814,9 @@
       <c r="AU29" t="n">
         <v>37.38</v>
       </c>
+      <c r="AV29" t="n">
+        <v>37.33</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -4873,6 +4962,9 @@
       <c r="AU30" t="n">
         <v>56.65</v>
       </c>
+      <c r="AV30" t="n">
+        <v>56.65</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -5018,6 +5110,9 @@
       <c r="AU31" t="n">
         <v>28.19</v>
       </c>
+      <c r="AV31" t="n">
+        <v>28.19</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -5163,6 +5258,9 @@
       <c r="AU32" t="n">
         <v>50.5</v>
       </c>
+      <c r="AV32" t="n">
+        <v>50.5</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -5308,6 +5406,9 @@
       <c r="AU33" t="n">
         <v>47.33</v>
       </c>
+      <c r="AV33" t="n">
+        <v>47.33</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -5451,6 +5552,9 @@
         <v>44.5</v>
       </c>
       <c r="AU34" t="n">
+        <v>44.36</v>
+      </c>
+      <c r="AV34" t="n">
         <v>44.36</v>
       </c>
     </row>

--- a/gaa_rankings_pivot.xlsx
+++ b/gaa_rankings_pivot.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV34"/>
+  <dimension ref="A1:AW34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -673,6 +673,11 @@
           <t>2026-04-28</t>
         </is>
       </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -821,6 +826,9 @@
       <c r="AV2" t="n">
         <v>39.18</v>
       </c>
+      <c r="AW2" t="n">
+        <v>39.18</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -969,6 +977,9 @@
       <c r="AV3" t="n">
         <v>62.77</v>
       </c>
+      <c r="AW3" t="n">
+        <v>63.98</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1117,6 +1128,9 @@
       <c r="AV4" t="n">
         <v>38.29</v>
       </c>
+      <c r="AW4" t="n">
+        <v>38.29</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1265,6 +1279,9 @@
       <c r="AV5" t="n">
         <v>51.23</v>
       </c>
+      <c r="AW5" t="n">
+        <v>51.23</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1413,6 +1430,9 @@
       <c r="AV6" t="n">
         <v>46.92</v>
       </c>
+      <c r="AW6" t="n">
+        <v>46.92</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1561,6 +1581,9 @@
       <c r="AV7" t="n">
         <v>58.54</v>
       </c>
+      <c r="AW7" t="n">
+        <v>58.54</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1709,6 +1732,9 @@
       <c r="AV8" t="n">
         <v>58.89</v>
       </c>
+      <c r="AW8" t="n">
+        <v>56.83</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1857,6 +1883,9 @@
       <c r="AV9" t="n">
         <v>64.09999999999999</v>
       </c>
+      <c r="AW9" t="n">
+        <v>64.09999999999999</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2005,6 +2034,9 @@
       <c r="AV10" t="n">
         <v>58.41</v>
       </c>
+      <c r="AW10" t="n">
+        <v>57.2</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2153,6 +2185,9 @@
       <c r="AV11" t="n">
         <v>59.87</v>
       </c>
+      <c r="AW11" t="n">
+        <v>61.82</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2301,6 +2336,9 @@
       <c r="AV12" t="n">
         <v>43.08</v>
       </c>
+      <c r="AW12" t="n">
+        <v>43.08</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2449,6 +2487,9 @@
       <c r="AV13" t="n">
         <v>63.53</v>
       </c>
+      <c r="AW13" t="n">
+        <v>63.53</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2597,6 +2638,9 @@
       <c r="AV14" t="n">
         <v>67.09</v>
       </c>
+      <c r="AW14" t="n">
+        <v>67.09</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2745,6 +2789,9 @@
       <c r="AV15" t="n">
         <v>51.74</v>
       </c>
+      <c r="AW15" t="n">
+        <v>50.03</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2893,6 +2940,9 @@
       <c r="AV16" t="n">
         <v>48.28</v>
       </c>
+      <c r="AW16" t="n">
+        <v>48.28</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -3041,6 +3091,9 @@
       <c r="AV17" t="n">
         <v>40.09</v>
       </c>
+      <c r="AW17" t="n">
+        <v>40.09</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -3189,6 +3242,9 @@
       <c r="AV18" t="n">
         <v>45.1</v>
       </c>
+      <c r="AW18" t="n">
+        <v>45.1</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -3337,6 +3393,9 @@
       <c r="AV19" t="n">
         <v>35.24</v>
       </c>
+      <c r="AW19" t="n">
+        <v>35.24</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -3485,6 +3544,9 @@
       <c r="AV20" t="n">
         <v>36.01</v>
       </c>
+      <c r="AW20" t="n">
+        <v>36.01</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -3633,6 +3695,9 @@
       <c r="AV21" t="n">
         <v>58.72</v>
       </c>
+      <c r="AW21" t="n">
+        <v>56.77</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -3781,6 +3846,9 @@
       <c r="AV22" t="n">
         <v>59.8</v>
       </c>
+      <c r="AW22" t="n">
+        <v>59.8</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -3929,6 +3997,9 @@
       <c r="AV23" t="n">
         <v>59.92</v>
       </c>
+      <c r="AW23" t="n">
+        <v>59.92</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -4077,6 +4148,9 @@
       <c r="AV24" t="n">
         <v>55.49</v>
       </c>
+      <c r="AW24" t="n">
+        <v>57.55</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -4225,6 +4299,9 @@
       <c r="AV25" t="n">
         <v>36.67</v>
       </c>
+      <c r="AW25" t="n">
+        <v>36.67</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -4373,6 +4450,9 @@
       <c r="AV26" t="n">
         <v>42.26</v>
       </c>
+      <c r="AW26" t="n">
+        <v>42.26</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -4521,6 +4601,9 @@
       <c r="AV27" t="n">
         <v>61.13</v>
       </c>
+      <c r="AW27" t="n">
+        <v>61.13</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -4669,6 +4752,9 @@
       <c r="AV28" t="n">
         <v>43.29</v>
       </c>
+      <c r="AW28" t="n">
+        <v>43.29</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -4817,6 +4903,9 @@
       <c r="AV29" t="n">
         <v>37.33</v>
       </c>
+      <c r="AW29" t="n">
+        <v>37.33</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -4965,6 +5054,9 @@
       <c r="AV30" t="n">
         <v>56.65</v>
       </c>
+      <c r="AW30" t="n">
+        <v>56.65</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -5113,6 +5205,9 @@
       <c r="AV31" t="n">
         <v>28.19</v>
       </c>
+      <c r="AW31" t="n">
+        <v>28.19</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -5261,6 +5356,9 @@
       <c r="AV32" t="n">
         <v>50.5</v>
       </c>
+      <c r="AW32" t="n">
+        <v>52.21</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -5409,6 +5507,9 @@
       <c r="AV33" t="n">
         <v>47.33</v>
       </c>
+      <c r="AW33" t="n">
+        <v>47.33</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -5555,6 +5656,9 @@
         <v>44.36</v>
       </c>
       <c r="AV34" t="n">
+        <v>44.36</v>
+      </c>
+      <c r="AW34" t="n">
         <v>44.36</v>
       </c>
     </row>

--- a/gaa_rankings_pivot.xlsx
+++ b/gaa_rankings_pivot.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW34"/>
+  <dimension ref="A1:AX34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,6 +678,11 @@
           <t>2026-05-05</t>
         </is>
       </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -829,6 +834,9 @@
       <c r="AW2" t="n">
         <v>39.18</v>
       </c>
+      <c r="AX2" t="n">
+        <v>40.87</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -980,6 +988,9 @@
       <c r="AW3" t="n">
         <v>63.98</v>
       </c>
+      <c r="AX3" t="n">
+        <v>63.98</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1131,6 +1142,9 @@
       <c r="AW4" t="n">
         <v>38.29</v>
       </c>
+      <c r="AX4" t="n">
+        <v>36.6</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1282,6 +1296,9 @@
       <c r="AW5" t="n">
         <v>51.23</v>
       </c>
+      <c r="AX5" t="n">
+        <v>51.23</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1433,6 +1450,9 @@
       <c r="AW6" t="n">
         <v>46.92</v>
       </c>
+      <c r="AX6" t="n">
+        <v>44.45</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1584,6 +1604,9 @@
       <c r="AW7" t="n">
         <v>58.54</v>
       </c>
+      <c r="AX7" t="n">
+        <v>58.3</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1735,6 +1758,9 @@
       <c r="AW8" t="n">
         <v>56.83</v>
       </c>
+      <c r="AX8" t="n">
+        <v>56.83</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1886,6 +1912,9 @@
       <c r="AW9" t="n">
         <v>64.09999999999999</v>
       </c>
+      <c r="AX9" t="n">
+        <v>64.09999999999999</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2037,6 +2066,9 @@
       <c r="AW10" t="n">
         <v>57.2</v>
       </c>
+      <c r="AX10" t="n">
+        <v>57.2</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2188,6 +2220,9 @@
       <c r="AW11" t="n">
         <v>61.82</v>
       </c>
+      <c r="AX11" t="n">
+        <v>61.82</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2339,6 +2374,9 @@
       <c r="AW12" t="n">
         <v>43.08</v>
       </c>
+      <c r="AX12" t="n">
+        <v>43.41</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2490,6 +2528,9 @@
       <c r="AW13" t="n">
         <v>63.53</v>
       </c>
+      <c r="AX13" t="n">
+        <v>61.96</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2641,6 +2682,9 @@
       <c r="AW14" t="n">
         <v>67.09</v>
       </c>
+      <c r="AX14" t="n">
+        <v>67.33</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2792,6 +2836,9 @@
       <c r="AW15" t="n">
         <v>50.03</v>
       </c>
+      <c r="AX15" t="n">
+        <v>50.03</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2943,6 +2990,9 @@
       <c r="AW16" t="n">
         <v>48.28</v>
       </c>
+      <c r="AX16" t="n">
+        <v>48.89</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -3094,6 +3144,9 @@
       <c r="AW17" t="n">
         <v>40.09</v>
       </c>
+      <c r="AX17" t="n">
+        <v>40.09</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -3245,6 +3298,9 @@
       <c r="AW18" t="n">
         <v>45.1</v>
       </c>
+      <c r="AX18" t="n">
+        <v>43.87</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -3396,6 +3452,9 @@
       <c r="AW19" t="n">
         <v>35.24</v>
       </c>
+      <c r="AX19" t="n">
+        <v>36.31</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -3547,6 +3606,9 @@
       <c r="AW20" t="n">
         <v>36.01</v>
       </c>
+      <c r="AX20" t="n">
+        <v>35.68</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -3698,6 +3760,9 @@
       <c r="AW21" t="n">
         <v>56.77</v>
       </c>
+      <c r="AX21" t="n">
+        <v>56.77</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -3849,6 +3914,9 @@
       <c r="AW22" t="n">
         <v>59.8</v>
       </c>
+      <c r="AX22" t="n">
+        <v>59.8</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -4000,6 +4068,9 @@
       <c r="AW23" t="n">
         <v>59.92</v>
       </c>
+      <c r="AX23" t="n">
+        <v>59.92</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -4151,6 +4222,9 @@
       <c r="AW24" t="n">
         <v>57.55</v>
       </c>
+      <c r="AX24" t="n">
+        <v>57.55</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -4302,6 +4376,9 @@
       <c r="AW25" t="n">
         <v>36.67</v>
       </c>
+      <c r="AX25" t="n">
+        <v>36.67</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -4453,6 +4530,9 @@
       <c r="AW26" t="n">
         <v>42.26</v>
       </c>
+      <c r="AX26" t="n">
+        <v>44.73</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -4604,6 +4684,9 @@
       <c r="AW27" t="n">
         <v>61.13</v>
       </c>
+      <c r="AX27" t="n">
+        <v>62.7</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -4755,6 +4838,9 @@
       <c r="AW28" t="n">
         <v>43.29</v>
       </c>
+      <c r="AX28" t="n">
+        <v>40.7</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -4906,6 +4992,9 @@
       <c r="AW29" t="n">
         <v>37.33</v>
       </c>
+      <c r="AX29" t="n">
+        <v>39.92</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -5057,6 +5146,9 @@
       <c r="AW30" t="n">
         <v>56.65</v>
       </c>
+      <c r="AX30" t="n">
+        <v>56.65</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -5208,6 +5300,9 @@
       <c r="AW31" t="n">
         <v>28.19</v>
       </c>
+      <c r="AX31" t="n">
+        <v>27.12</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -5359,6 +5454,9 @@
       <c r="AW32" t="n">
         <v>52.21</v>
       </c>
+      <c r="AX32" t="n">
+        <v>52.21</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -5510,6 +5608,9 @@
       <c r="AW33" t="n">
         <v>47.33</v>
       </c>
+      <c r="AX33" t="n">
+        <v>48.56</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -5660,6 +5761,9 @@
       </c>
       <c r="AW34" t="n">
         <v>44.36</v>
+      </c>
+      <c r="AX34" t="n">
+        <v>43.75</v>
       </c>
     </row>
   </sheetData>

--- a/gaa_rankings_pivot.xlsx
+++ b/gaa_rankings_pivot.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX34"/>
+  <dimension ref="A1:AY34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -683,6 +683,11 @@
           <t>2026-05-12</t>
         </is>
       </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -837,6 +842,9 @@
       <c r="AX2" t="n">
         <v>40.87</v>
       </c>
+      <c r="AY2" t="n">
+        <v>40.87</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -991,6 +999,9 @@
       <c r="AX3" t="n">
         <v>63.98</v>
       </c>
+      <c r="AY3" t="n">
+        <v>65.17</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1145,6 +1156,9 @@
       <c r="AX4" t="n">
         <v>36.6</v>
       </c>
+      <c r="AY4" t="n">
+        <v>36.6</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1299,6 +1313,9 @@
       <c r="AX5" t="n">
         <v>51.23</v>
       </c>
+      <c r="AY5" t="n">
+        <v>51.23</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1453,6 +1470,9 @@
       <c r="AX6" t="n">
         <v>44.45</v>
       </c>
+      <c r="AY6" t="n">
+        <v>44.45</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1607,6 +1627,9 @@
       <c r="AX7" t="n">
         <v>58.3</v>
       </c>
+      <c r="AY7" t="n">
+        <v>58.3</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1761,6 +1784,9 @@
       <c r="AX8" t="n">
         <v>56.83</v>
       </c>
+      <c r="AY8" t="n">
+        <v>56.83</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1915,6 +1941,9 @@
       <c r="AX9" t="n">
         <v>64.09999999999999</v>
       </c>
+      <c r="AY9" t="n">
+        <v>64.09999999999999</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2069,6 +2098,9 @@
       <c r="AX10" t="n">
         <v>57.2</v>
       </c>
+      <c r="AY10" t="n">
+        <v>57.25</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2223,6 +2255,9 @@
       <c r="AX11" t="n">
         <v>61.82</v>
       </c>
+      <c r="AY11" t="n">
+        <v>59.01</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2377,6 +2412,9 @@
       <c r="AX12" t="n">
         <v>43.41</v>
       </c>
+      <c r="AY12" t="n">
+        <v>43.41</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2531,6 +2569,9 @@
       <c r="AX13" t="n">
         <v>61.96</v>
       </c>
+      <c r="AY13" t="n">
+        <v>61.96</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2685,6 +2726,9 @@
       <c r="AX14" t="n">
         <v>67.33</v>
       </c>
+      <c r="AY14" t="n">
+        <v>67.33</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2839,6 +2883,9 @@
       <c r="AX15" t="n">
         <v>50.03</v>
       </c>
+      <c r="AY15" t="n">
+        <v>50.03</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2993,6 +3040,9 @@
       <c r="AX16" t="n">
         <v>48.89</v>
       </c>
+      <c r="AY16" t="n">
+        <v>48.89</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -3147,6 +3197,9 @@
       <c r="AX17" t="n">
         <v>40.09</v>
       </c>
+      <c r="AY17" t="n">
+        <v>40.04</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -3301,6 +3354,9 @@
       <c r="AX18" t="n">
         <v>43.87</v>
       </c>
+      <c r="AY18" t="n">
+        <v>43.87</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -3455,6 +3511,9 @@
       <c r="AX19" t="n">
         <v>36.31</v>
       </c>
+      <c r="AY19" t="n">
+        <v>36.31</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -3609,6 +3668,9 @@
       <c r="AX20" t="n">
         <v>35.68</v>
       </c>
+      <c r="AY20" t="n">
+        <v>35.68</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -3763,6 +3825,9 @@
       <c r="AX21" t="n">
         <v>56.77</v>
       </c>
+      <c r="AY21" t="n">
+        <v>56.77</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -3917,6 +3982,9 @@
       <c r="AX22" t="n">
         <v>59.8</v>
       </c>
+      <c r="AY22" t="n">
+        <v>59.8</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -4071,6 +4139,9 @@
       <c r="AX23" t="n">
         <v>59.92</v>
       </c>
+      <c r="AY23" t="n">
+        <v>59.92</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -4225,6 +4296,9 @@
       <c r="AX24" t="n">
         <v>57.55</v>
       </c>
+      <c r="AY24" t="n">
+        <v>56.36</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -4379,6 +4453,9 @@
       <c r="AX25" t="n">
         <v>36.67</v>
       </c>
+      <c r="AY25" t="n">
+        <v>36.67</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -4533,6 +4610,9 @@
       <c r="AX26" t="n">
         <v>44.73</v>
       </c>
+      <c r="AY26" t="n">
+        <v>44.73</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -4687,6 +4767,9 @@
       <c r="AX27" t="n">
         <v>62.7</v>
       </c>
+      <c r="AY27" t="n">
+        <v>62.7</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -4841,6 +4924,9 @@
       <c r="AX28" t="n">
         <v>40.7</v>
       </c>
+      <c r="AY28" t="n">
+        <v>40.7</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -4995,6 +5081,9 @@
       <c r="AX29" t="n">
         <v>39.92</v>
       </c>
+      <c r="AY29" t="n">
+        <v>39.92</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -5149,6 +5238,9 @@
       <c r="AX30" t="n">
         <v>56.65</v>
       </c>
+      <c r="AY30" t="n">
+        <v>56.65</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -5303,6 +5395,9 @@
       <c r="AX31" t="n">
         <v>27.12</v>
       </c>
+      <c r="AY31" t="n">
+        <v>27.12</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -5457,6 +5552,9 @@
       <c r="AX32" t="n">
         <v>52.21</v>
       </c>
+      <c r="AY32" t="n">
+        <v>55.02</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -5611,6 +5709,9 @@
       <c r="AX33" t="n">
         <v>48.56</v>
       </c>
+      <c r="AY33" t="n">
+        <v>48.56</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -5763,6 +5864,9 @@
         <v>44.36</v>
       </c>
       <c r="AX34" t="n">
+        <v>43.75</v>
+      </c>
+      <c r="AY34" t="n">
         <v>43.75</v>
       </c>
     </row>

--- a/gaa_rankings_pivot.xlsx
+++ b/gaa_rankings_pivot.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY34"/>
+  <dimension ref="A1:AZ34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -688,6 +688,11 @@
           <t>2026-05-19</t>
         </is>
       </c>
+      <c r="AZ1" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -845,6 +850,9 @@
       <c r="AY2" t="n">
         <v>40.87</v>
       </c>
+      <c r="AZ2" t="n">
+        <v>41.88</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1002,6 +1010,9 @@
       <c r="AY3" t="n">
         <v>65.17</v>
       </c>
+      <c r="AZ3" t="n">
+        <v>65.17</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1159,6 +1170,9 @@
       <c r="AY4" t="n">
         <v>36.6</v>
       </c>
+      <c r="AZ4" t="n">
+        <v>35.93</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1316,6 +1330,9 @@
       <c r="AY5" t="n">
         <v>51.23</v>
       </c>
+      <c r="AZ5" t="n">
+        <v>51.23</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1473,6 +1490,9 @@
       <c r="AY6" t="n">
         <v>44.45</v>
       </c>
+      <c r="AZ6" t="n">
+        <v>41.68</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1630,6 +1650,9 @@
       <c r="AY7" t="n">
         <v>58.3</v>
       </c>
+      <c r="AZ7" t="n">
+        <v>59.73</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1787,6 +1810,9 @@
       <c r="AY8" t="n">
         <v>56.83</v>
       </c>
+      <c r="AZ8" t="n">
+        <v>56.83</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1944,6 +1970,9 @@
       <c r="AY9" t="n">
         <v>64.09999999999999</v>
       </c>
+      <c r="AZ9" t="n">
+        <v>67.56</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2101,6 +2130,9 @@
       <c r="AY10" t="n">
         <v>57.25</v>
       </c>
+      <c r="AZ10" t="n">
+        <v>54.49</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2258,6 +2290,9 @@
       <c r="AY11" t="n">
         <v>59.01</v>
       </c>
+      <c r="AZ11" t="n">
+        <v>59.01</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2415,6 +2450,9 @@
       <c r="AY12" t="n">
         <v>43.41</v>
       </c>
+      <c r="AZ12" t="n">
+        <v>45.43</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2572,6 +2610,9 @@
       <c r="AY13" t="n">
         <v>61.96</v>
       </c>
+      <c r="AZ13" t="n">
+        <v>62.13</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2729,6 +2770,9 @@
       <c r="AY14" t="n">
         <v>67.33</v>
       </c>
+      <c r="AZ14" t="n">
+        <v>63.87</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2886,6 +2930,9 @@
       <c r="AY15" t="n">
         <v>50.03</v>
       </c>
+      <c r="AZ15" t="n">
+        <v>49.86</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -3043,6 +3090,9 @@
       <c r="AY16" t="n">
         <v>48.89</v>
       </c>
+      <c r="AZ16" t="n">
+        <v>49.25</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -3200,6 +3250,9 @@
       <c r="AY17" t="n">
         <v>40.04</v>
       </c>
+      <c r="AZ17" t="n">
+        <v>40.71</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -3357,6 +3410,9 @@
       <c r="AY18" t="n">
         <v>43.87</v>
       </c>
+      <c r="AZ18" t="n">
+        <v>42.1</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -3514,6 +3570,9 @@
       <c r="AY19" t="n">
         <v>36.31</v>
       </c>
+      <c r="AZ19" t="n">
+        <v>35.95</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -3671,6 +3730,9 @@
       <c r="AY20" t="n">
         <v>35.68</v>
       </c>
+      <c r="AZ20" t="n">
+        <v>38.45</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -3828,6 +3890,9 @@
       <c r="AY21" t="n">
         <v>56.77</v>
       </c>
+      <c r="AZ21" t="n">
+        <v>56.77</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -3985,6 +4050,9 @@
       <c r="AY22" t="n">
         <v>59.8</v>
       </c>
+      <c r="AZ22" t="n">
+        <v>59.8</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -4142,6 +4210,9 @@
       <c r="AY23" t="n">
         <v>59.92</v>
       </c>
+      <c r="AZ23" t="n">
+        <v>58.49</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -4299,6 +4370,9 @@
       <c r="AY24" t="n">
         <v>56.36</v>
       </c>
+      <c r="AZ24" t="n">
+        <v>56.36</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -4456,6 +4530,9 @@
       <c r="AY25" t="n">
         <v>36.67</v>
       </c>
+      <c r="AZ25" t="n">
+        <v>36.67</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -4613,6 +4690,9 @@
       <c r="AY26" t="n">
         <v>44.73</v>
       </c>
+      <c r="AZ26" t="n">
+        <v>47.49</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -4770,6 +4850,9 @@
       <c r="AY27" t="n">
         <v>62.7</v>
       </c>
+      <c r="AZ27" t="n">
+        <v>60.11</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -4927,6 +5010,9 @@
       <c r="AY28" t="n">
         <v>40.7</v>
       </c>
+      <c r="AZ28" t="n">
+        <v>40.89</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -5084,6 +5170,9 @@
       <c r="AY29" t="n">
         <v>39.92</v>
       </c>
+      <c r="AZ29" t="n">
+        <v>38.91</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -5241,6 +5330,9 @@
       <c r="AY30" t="n">
         <v>56.65</v>
       </c>
+      <c r="AZ30" t="n">
+        <v>59.24</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -5398,6 +5490,9 @@
       <c r="AY31" t="n">
         <v>27.12</v>
       </c>
+      <c r="AZ31" t="n">
+        <v>26.93</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -5555,6 +5650,9 @@
       <c r="AY32" t="n">
         <v>55.02</v>
       </c>
+      <c r="AZ32" t="n">
+        <v>55.02</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -5712,6 +5810,9 @@
       <c r="AY33" t="n">
         <v>48.56</v>
       </c>
+      <c r="AZ33" t="n">
+        <v>46.54</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -5868,6 +5969,9 @@
       </c>
       <c r="AY34" t="n">
         <v>43.75</v>
+      </c>
+      <c r="AZ34" t="n">
+        <v>45.52</v>
       </c>
     </row>
   </sheetData>

--- a/gaa_rankings_pivot.xlsx
+++ b/gaa_rankings_pivot.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ34"/>
+  <dimension ref="A1:BA34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -693,6 +693,11 @@
           <t>2026-05-28</t>
         </is>
       </c>
+      <c r="BA1" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -853,6 +858,9 @@
       <c r="AZ2" t="n">
         <v>41.88</v>
       </c>
+      <c r="BA2" t="n">
+        <v>41.88</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1013,6 +1021,9 @@
       <c r="AZ3" t="n">
         <v>65.17</v>
       </c>
+      <c r="BA3" t="n">
+        <v>65.42</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1173,6 +1184,9 @@
       <c r="AZ4" t="n">
         <v>35.93</v>
       </c>
+      <c r="BA4" t="n">
+        <v>35.93</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1333,6 +1347,9 @@
       <c r="AZ5" t="n">
         <v>51.23</v>
       </c>
+      <c r="BA5" t="n">
+        <v>50.6</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1493,6 +1510,9 @@
       <c r="AZ6" t="n">
         <v>41.68</v>
       </c>
+      <c r="BA6" t="n">
+        <v>41.68</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1653,6 +1673,9 @@
       <c r="AZ7" t="n">
         <v>59.73</v>
       </c>
+      <c r="BA7" t="n">
+        <v>59.73</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1813,6 +1836,9 @@
       <c r="AZ8" t="n">
         <v>56.83</v>
       </c>
+      <c r="BA8" t="n">
+        <v>56.58</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1973,6 +1999,9 @@
       <c r="AZ9" t="n">
         <v>67.56</v>
       </c>
+      <c r="BA9" t="n">
+        <v>67.56</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2133,6 +2162,9 @@
       <c r="AZ10" t="n">
         <v>54.49</v>
       </c>
+      <c r="BA10" t="n">
+        <v>54.66</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2293,6 +2325,9 @@
       <c r="AZ11" t="n">
         <v>59.01</v>
       </c>
+      <c r="BA11" t="n">
+        <v>56.83</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2453,6 +2488,9 @@
       <c r="AZ12" t="n">
         <v>45.43</v>
       </c>
+      <c r="BA12" t="n">
+        <v>45.78</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2613,6 +2651,9 @@
       <c r="AZ13" t="n">
         <v>62.13</v>
       </c>
+      <c r="BA13" t="n">
+        <v>62.13</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2773,6 +2814,9 @@
       <c r="AZ14" t="n">
         <v>63.87</v>
       </c>
+      <c r="BA14" t="n">
+        <v>63.87</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2933,6 +2977,9 @@
       <c r="AZ15" t="n">
         <v>49.86</v>
       </c>
+      <c r="BA15" t="n">
+        <v>49.86</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -3093,6 +3140,9 @@
       <c r="AZ16" t="n">
         <v>49.25</v>
       </c>
+      <c r="BA16" t="n">
+        <v>49.25</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -3253,6 +3303,9 @@
       <c r="AZ17" t="n">
         <v>40.71</v>
       </c>
+      <c r="BA17" t="n">
+        <v>39.83</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -3413,6 +3466,9 @@
       <c r="AZ18" t="n">
         <v>42.1</v>
       </c>
+      <c r="BA18" t="n">
+        <v>42.1</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -3573,6 +3629,9 @@
       <c r="AZ19" t="n">
         <v>35.95</v>
       </c>
+      <c r="BA19" t="n">
+        <v>34.94</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -3733,6 +3792,9 @@
       <c r="AZ20" t="n">
         <v>38.45</v>
       </c>
+      <c r="BA20" t="n">
+        <v>38.28</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -3893,6 +3955,9 @@
       <c r="AZ21" t="n">
         <v>56.77</v>
       </c>
+      <c r="BA21" t="n">
+        <v>58.95</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -4053,6 +4118,9 @@
       <c r="AZ22" t="n">
         <v>59.8</v>
       </c>
+      <c r="BA22" t="n">
+        <v>61.05</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -4213,6 +4281,9 @@
       <c r="AZ23" t="n">
         <v>58.49</v>
       </c>
+      <c r="BA23" t="n">
+        <v>58.49</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -4373,6 +4444,9 @@
       <c r="AZ24" t="n">
         <v>56.36</v>
       </c>
+      <c r="BA24" t="n">
+        <v>55.11</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -4533,6 +4607,9 @@
       <c r="AZ25" t="n">
         <v>36.67</v>
       </c>
+      <c r="BA25" t="n">
+        <v>36.32</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -4693,6 +4770,9 @@
       <c r="AZ26" t="n">
         <v>47.49</v>
       </c>
+      <c r="BA26" t="n">
+        <v>47.49</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -4853,6 +4933,9 @@
       <c r="AZ27" t="n">
         <v>60.11</v>
       </c>
+      <c r="BA27" t="n">
+        <v>60.11</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -5013,6 +5096,9 @@
       <c r="AZ28" t="n">
         <v>40.89</v>
       </c>
+      <c r="BA28" t="n">
+        <v>41.9</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -5173,6 +5259,9 @@
       <c r="AZ29" t="n">
         <v>38.91</v>
       </c>
+      <c r="BA29" t="n">
+        <v>38.55</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -5333,6 +5422,9 @@
       <c r="AZ30" t="n">
         <v>59.24</v>
       </c>
+      <c r="BA30" t="n">
+        <v>59.24</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -5493,6 +5585,9 @@
       <c r="AZ31" t="n">
         <v>26.93</v>
       </c>
+      <c r="BA31" t="n">
+        <v>26.93</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -5653,6 +5748,9 @@
       <c r="AZ32" t="n">
         <v>55.02</v>
       </c>
+      <c r="BA32" t="n">
+        <v>55.65</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -5813,6 +5911,9 @@
       <c r="AZ33" t="n">
         <v>46.54</v>
       </c>
+      <c r="BA33" t="n">
+        <v>47.42</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -5972,6 +6073,9 @@
       </c>
       <c r="AZ34" t="n">
         <v>45.52</v>
+      </c>
+      <c r="BA34" t="n">
+        <v>45.88</v>
       </c>
     </row>
   </sheetData>

--- a/gaa_rankings_pivot.xlsx
+++ b/gaa_rankings_pivot.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BA34"/>
+  <dimension ref="A1:BB34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -698,6 +698,11 @@
           <t>2026-06-08</t>
         </is>
       </c>
+      <c r="BB1" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -861,6 +866,9 @@
       <c r="BA2" t="n">
         <v>41.88</v>
       </c>
+      <c r="BB2" t="n">
+        <v>41.88</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1024,6 +1032,9 @@
       <c r="BA3" t="n">
         <v>65.42</v>
       </c>
+      <c r="BB3" t="n">
+        <v>65.42</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1187,6 +1198,9 @@
       <c r="BA4" t="n">
         <v>35.93</v>
       </c>
+      <c r="BB4" t="n">
+        <v>35.93</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1350,6 +1364,9 @@
       <c r="BA5" t="n">
         <v>50.6</v>
       </c>
+      <c r="BB5" t="n">
+        <v>50.6</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1513,6 +1530,9 @@
       <c r="BA6" t="n">
         <v>41.68</v>
       </c>
+      <c r="BB6" t="n">
+        <v>41.68</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1676,6 +1696,9 @@
       <c r="BA7" t="n">
         <v>59.73</v>
       </c>
+      <c r="BB7" t="n">
+        <v>59.73</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1839,6 +1862,9 @@
       <c r="BA8" t="n">
         <v>56.58</v>
       </c>
+      <c r="BB8" t="n">
+        <v>56.58</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2002,6 +2028,9 @@
       <c r="BA9" t="n">
         <v>67.56</v>
       </c>
+      <c r="BB9" t="n">
+        <v>67.56</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2165,6 +2194,9 @@
       <c r="BA10" t="n">
         <v>54.66</v>
       </c>
+      <c r="BB10" t="n">
+        <v>54.66</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2328,6 +2360,9 @@
       <c r="BA11" t="n">
         <v>56.83</v>
       </c>
+      <c r="BB11" t="n">
+        <v>56.83</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2491,6 +2526,9 @@
       <c r="BA12" t="n">
         <v>45.78</v>
       </c>
+      <c r="BB12" t="n">
+        <v>45.78</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2654,6 +2692,9 @@
       <c r="BA13" t="n">
         <v>62.13</v>
       </c>
+      <c r="BB13" t="n">
+        <v>62.13</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2817,6 +2858,9 @@
       <c r="BA14" t="n">
         <v>63.87</v>
       </c>
+      <c r="BB14" t="n">
+        <v>63.87</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2980,6 +3024,9 @@
       <c r="BA15" t="n">
         <v>49.86</v>
       </c>
+      <c r="BB15" t="n">
+        <v>49.86</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -3143,6 +3190,9 @@
       <c r="BA16" t="n">
         <v>49.25</v>
       </c>
+      <c r="BB16" t="n">
+        <v>49.25</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -3306,6 +3356,9 @@
       <c r="BA17" t="n">
         <v>39.83</v>
       </c>
+      <c r="BB17" t="n">
+        <v>39.83</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -3469,6 +3522,9 @@
       <c r="BA18" t="n">
         <v>42.1</v>
       </c>
+      <c r="BB18" t="n">
+        <v>42.1</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -3632,6 +3688,9 @@
       <c r="BA19" t="n">
         <v>34.94</v>
       </c>
+      <c r="BB19" t="n">
+        <v>34.94</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -3795,6 +3854,9 @@
       <c r="BA20" t="n">
         <v>38.28</v>
       </c>
+      <c r="BB20" t="n">
+        <v>38.28</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -3958,6 +4020,9 @@
       <c r="BA21" t="n">
         <v>58.95</v>
       </c>
+      <c r="BB21" t="n">
+        <v>58.95</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -4121,6 +4186,9 @@
       <c r="BA22" t="n">
         <v>61.05</v>
       </c>
+      <c r="BB22" t="n">
+        <v>61.05</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -4284,6 +4352,9 @@
       <c r="BA23" t="n">
         <v>58.49</v>
       </c>
+      <c r="BB23" t="n">
+        <v>58.49</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -4447,6 +4518,9 @@
       <c r="BA24" t="n">
         <v>55.11</v>
       </c>
+      <c r="BB24" t="n">
+        <v>55.11</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -4610,6 +4684,9 @@
       <c r="BA25" t="n">
         <v>36.32</v>
       </c>
+      <c r="BB25" t="n">
+        <v>36.32</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -4773,6 +4850,9 @@
       <c r="BA26" t="n">
         <v>47.49</v>
       </c>
+      <c r="BB26" t="n">
+        <v>47.49</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -4936,6 +5016,9 @@
       <c r="BA27" t="n">
         <v>60.11</v>
       </c>
+      <c r="BB27" t="n">
+        <v>60.11</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -5099,6 +5182,9 @@
       <c r="BA28" t="n">
         <v>41.9</v>
       </c>
+      <c r="BB28" t="n">
+        <v>41.9</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -5262,6 +5348,9 @@
       <c r="BA29" t="n">
         <v>38.55</v>
       </c>
+      <c r="BB29" t="n">
+        <v>38.55</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -5425,6 +5514,9 @@
       <c r="BA30" t="n">
         <v>59.24</v>
       </c>
+      <c r="BB30" t="n">
+        <v>59.24</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -5588,6 +5680,9 @@
       <c r="BA31" t="n">
         <v>26.93</v>
       </c>
+      <c r="BB31" t="n">
+        <v>26.93</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -5751,6 +5846,9 @@
       <c r="BA32" t="n">
         <v>55.65</v>
       </c>
+      <c r="BB32" t="n">
+        <v>55.65</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -5914,6 +6012,9 @@
       <c r="BA33" t="n">
         <v>47.42</v>
       </c>
+      <c r="BB33" t="n">
+        <v>47.42</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -6075,6 +6176,9 @@
         <v>45.52</v>
       </c>
       <c r="BA34" t="n">
+        <v>45.88</v>
+      </c>
+      <c r="BB34" t="n">
         <v>45.88</v>
       </c>
     </row>

--- a/gaa_rankings_pivot.xlsx
+++ b/gaa_rankings_pivot.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BB34"/>
+  <dimension ref="A1:BC34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -703,6 +703,11 @@
           <t>2026-06-09</t>
         </is>
       </c>
+      <c r="BC1" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -869,6 +874,9 @@
       <c r="BB2" t="n">
         <v>41.88</v>
       </c>
+      <c r="BC2" t="n">
+        <v>40.72</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1035,6 +1043,9 @@
       <c r="BB3" t="n">
         <v>65.42</v>
       </c>
+      <c r="BC3" t="n">
+        <v>62.97</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1201,6 +1212,9 @@
       <c r="BB4" t="n">
         <v>35.93</v>
       </c>
+      <c r="BC4" t="n">
+        <v>35.93</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1367,6 +1381,9 @@
       <c r="BB5" t="n">
         <v>50.6</v>
       </c>
+      <c r="BC5" t="n">
+        <v>49.37</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1533,6 +1550,9 @@
       <c r="BB6" t="n">
         <v>41.68</v>
       </c>
+      <c r="BC6" t="n">
+        <v>41.68</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1699,6 +1719,9 @@
       <c r="BB7" t="n">
         <v>59.73</v>
       </c>
+      <c r="BC7" t="n">
+        <v>62.45</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1865,6 +1888,9 @@
       <c r="BB8" t="n">
         <v>56.58</v>
       </c>
+      <c r="BC8" t="n">
+        <v>55.06</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2031,6 +2057,9 @@
       <c r="BB9" t="n">
         <v>67.56</v>
       </c>
+      <c r="BC9" t="n">
+        <v>64.84</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2197,6 +2226,9 @@
       <c r="BB10" t="n">
         <v>54.66</v>
       </c>
+      <c r="BC10" t="n">
+        <v>56.07</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2363,6 +2395,9 @@
       <c r="BB11" t="n">
         <v>56.83</v>
       </c>
+      <c r="BC11" t="n">
+        <v>58.06</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2529,6 +2564,9 @@
       <c r="BB12" t="n">
         <v>45.78</v>
       </c>
+      <c r="BC12" t="n">
+        <v>46.7</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2695,6 +2733,9 @@
       <c r="BB13" t="n">
         <v>62.13</v>
       </c>
+      <c r="BC13" t="n">
+        <v>62.5</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2861,6 +2902,9 @@
       <c r="BB14" t="n">
         <v>63.87</v>
       </c>
+      <c r="BC14" t="n">
+        <v>64.14</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -3027,6 +3071,9 @@
       <c r="BB15" t="n">
         <v>49.86</v>
       </c>
+      <c r="BC15" t="n">
+        <v>49.59</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -3193,6 +3240,9 @@
       <c r="BB16" t="n">
         <v>49.25</v>
       </c>
+      <c r="BC16" t="n">
+        <v>47.84</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -3359,6 +3409,9 @@
       <c r="BB17" t="n">
         <v>39.83</v>
       </c>
+      <c r="BC17" t="n">
+        <v>39.83</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -3525,6 +3578,9 @@
       <c r="BB18" t="n">
         <v>42.1</v>
       </c>
+      <c r="BC18" t="n">
+        <v>42.1</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -3691,6 +3747,9 @@
       <c r="BB19" t="n">
         <v>34.94</v>
       </c>
+      <c r="BC19" t="n">
+        <v>34.94</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -3857,6 +3916,9 @@
       <c r="BB20" t="n">
         <v>38.28</v>
       </c>
+      <c r="BC20" t="n">
+        <v>38.28</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -4023,6 +4085,9 @@
       <c r="BB21" t="n">
         <v>58.95</v>
       </c>
+      <c r="BC21" t="n">
+        <v>61.4</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -4189,6 +4254,9 @@
       <c r="BB22" t="n">
         <v>61.05</v>
       </c>
+      <c r="BC22" t="n">
+        <v>59.58</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -4355,6 +4423,9 @@
       <c r="BB23" t="n">
         <v>58.49</v>
       </c>
+      <c r="BC23" t="n">
+        <v>60.01</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -4521,6 +4592,9 @@
       <c r="BB24" t="n">
         <v>55.11</v>
       </c>
+      <c r="BC24" t="n">
+        <v>58.11</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -4687,6 +4761,9 @@
       <c r="BB25" t="n">
         <v>36.32</v>
       </c>
+      <c r="BC25" t="n">
+        <v>36.32</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -4853,6 +4930,9 @@
       <c r="BB26" t="n">
         <v>47.49</v>
       </c>
+      <c r="BC26" t="n">
+        <v>48.64</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -5019,6 +5099,9 @@
       <c r="BB27" t="n">
         <v>60.11</v>
       </c>
+      <c r="BC27" t="n">
+        <v>57.11</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -5185,6 +5268,9 @@
       <c r="BB28" t="n">
         <v>41.9</v>
       </c>
+      <c r="BC28" t="n">
+        <v>40.98</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -5351,6 +5437,9 @@
       <c r="BB29" t="n">
         <v>38.55</v>
       </c>
+      <c r="BC29" t="n">
+        <v>38.55</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -5517,6 +5606,9 @@
       <c r="BB30" t="n">
         <v>59.24</v>
       </c>
+      <c r="BC30" t="n">
+        <v>60.71</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -5683,6 +5775,9 @@
       <c r="BB31" t="n">
         <v>26.93</v>
       </c>
+      <c r="BC31" t="n">
+        <v>26.93</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -5849,6 +5944,9 @@
       <c r="BB32" t="n">
         <v>55.65</v>
       </c>
+      <c r="BC32" t="n">
+        <v>55.28</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -6015,6 +6113,9 @@
       <c r="BB33" t="n">
         <v>47.42</v>
       </c>
+      <c r="BC33" t="n">
+        <v>46.27</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -6180,6 +6281,9 @@
       </c>
       <c r="BB34" t="n">
         <v>45.88</v>
+      </c>
+      <c r="BC34" t="n">
+        <v>47.04</v>
       </c>
     </row>
   </sheetData>

--- a/gaa_rankings_pivot.xlsx
+++ b/gaa_rankings_pivot.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BC34"/>
+  <dimension ref="A1:BD34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -708,6 +708,11 @@
           <t>2026-06-15</t>
         </is>
       </c>
+      <c r="BD1" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -877,6 +882,9 @@
       <c r="BC2" t="n">
         <v>40.72</v>
       </c>
+      <c r="BD2" t="n">
+        <v>40.72</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1046,6 +1054,9 @@
       <c r="BC3" t="n">
         <v>62.97</v>
       </c>
+      <c r="BD3" t="n">
+        <v>62.97</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1215,6 +1226,9 @@
       <c r="BC4" t="n">
         <v>35.93</v>
       </c>
+      <c r="BD4" t="n">
+        <v>35.93</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1384,6 +1398,9 @@
       <c r="BC5" t="n">
         <v>49.37</v>
       </c>
+      <c r="BD5" t="n">
+        <v>49.37</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1553,6 +1570,9 @@
       <c r="BC6" t="n">
         <v>41.68</v>
       </c>
+      <c r="BD6" t="n">
+        <v>41.68</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1722,6 +1742,9 @@
       <c r="BC7" t="n">
         <v>62.45</v>
       </c>
+      <c r="BD7" t="n">
+        <v>62.45</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1891,6 +1914,9 @@
       <c r="BC8" t="n">
         <v>55.06</v>
       </c>
+      <c r="BD8" t="n">
+        <v>55.06</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2060,6 +2086,9 @@
       <c r="BC9" t="n">
         <v>64.84</v>
       </c>
+      <c r="BD9" t="n">
+        <v>64.84</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2229,6 +2258,9 @@
       <c r="BC10" t="n">
         <v>56.07</v>
       </c>
+      <c r="BD10" t="n">
+        <v>56.07</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2398,6 +2430,9 @@
       <c r="BC11" t="n">
         <v>58.06</v>
       </c>
+      <c r="BD11" t="n">
+        <v>58.06</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2567,6 +2602,9 @@
       <c r="BC12" t="n">
         <v>46.7</v>
       </c>
+      <c r="BD12" t="n">
+        <v>46.7</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2736,6 +2774,9 @@
       <c r="BC13" t="n">
         <v>62.5</v>
       </c>
+      <c r="BD13" t="n">
+        <v>62.5</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2905,6 +2946,9 @@
       <c r="BC14" t="n">
         <v>64.14</v>
       </c>
+      <c r="BD14" t="n">
+        <v>64.14</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -3074,6 +3118,9 @@
       <c r="BC15" t="n">
         <v>49.59</v>
       </c>
+      <c r="BD15" t="n">
+        <v>49.59</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -3243,6 +3290,9 @@
       <c r="BC16" t="n">
         <v>47.84</v>
       </c>
+      <c r="BD16" t="n">
+        <v>47.84</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -3412,6 +3462,9 @@
       <c r="BC17" t="n">
         <v>39.83</v>
       </c>
+      <c r="BD17" t="n">
+        <v>39.83</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -3581,6 +3634,9 @@
       <c r="BC18" t="n">
         <v>42.1</v>
       </c>
+      <c r="BD18" t="n">
+        <v>42.1</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -3750,6 +3806,9 @@
       <c r="BC19" t="n">
         <v>34.94</v>
       </c>
+      <c r="BD19" t="n">
+        <v>34.94</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -3919,6 +3978,9 @@
       <c r="BC20" t="n">
         <v>38.28</v>
       </c>
+      <c r="BD20" t="n">
+        <v>38.28</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -4088,6 +4150,9 @@
       <c r="BC21" t="n">
         <v>61.4</v>
       </c>
+      <c r="BD21" t="n">
+        <v>61.4</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -4257,6 +4322,9 @@
       <c r="BC22" t="n">
         <v>59.58</v>
       </c>
+      <c r="BD22" t="n">
+        <v>59.58</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -4426,6 +4494,9 @@
       <c r="BC23" t="n">
         <v>60.01</v>
       </c>
+      <c r="BD23" t="n">
+        <v>60.01</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -4595,6 +4666,9 @@
       <c r="BC24" t="n">
         <v>58.11</v>
       </c>
+      <c r="BD24" t="n">
+        <v>58.11</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -4764,6 +4838,9 @@
       <c r="BC25" t="n">
         <v>36.32</v>
       </c>
+      <c r="BD25" t="n">
+        <v>36.32</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -4933,6 +5010,9 @@
       <c r="BC26" t="n">
         <v>48.64</v>
       </c>
+      <c r="BD26" t="n">
+        <v>48.64</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -5102,6 +5182,9 @@
       <c r="BC27" t="n">
         <v>57.11</v>
       </c>
+      <c r="BD27" t="n">
+        <v>57.11</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -5271,6 +5354,9 @@
       <c r="BC28" t="n">
         <v>40.98</v>
       </c>
+      <c r="BD28" t="n">
+        <v>40.98</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -5440,6 +5526,9 @@
       <c r="BC29" t="n">
         <v>38.55</v>
       </c>
+      <c r="BD29" t="n">
+        <v>38.55</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -5609,6 +5698,9 @@
       <c r="BC30" t="n">
         <v>60.71</v>
       </c>
+      <c r="BD30" t="n">
+        <v>60.71</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -5778,6 +5870,9 @@
       <c r="BC31" t="n">
         <v>26.93</v>
       </c>
+      <c r="BD31" t="n">
+        <v>26.93</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -5947,6 +6042,9 @@
       <c r="BC32" t="n">
         <v>55.28</v>
       </c>
+      <c r="BD32" t="n">
+        <v>55.28</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -6116,6 +6214,9 @@
       <c r="BC33" t="n">
         <v>46.27</v>
       </c>
+      <c r="BD33" t="n">
+        <v>46.27</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -6283,6 +6384,9 @@
         <v>45.88</v>
       </c>
       <c r="BC34" t="n">
+        <v>47.04</v>
+      </c>
+      <c r="BD34" t="n">
         <v>47.04</v>
       </c>
     </row>

--- a/gaa_rankings_pivot.xlsx
+++ b/gaa_rankings_pivot.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BD34"/>
+  <dimension ref="A1:BE34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -713,6 +713,11 @@
           <t>2026-06-16</t>
         </is>
       </c>
+      <c r="BE1" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -885,6 +890,9 @@
       <c r="BD2" t="n">
         <v>40.72</v>
       </c>
+      <c r="BE2" t="n">
+        <v>40.72</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1057,6 +1065,9 @@
       <c r="BD3" t="n">
         <v>62.97</v>
       </c>
+      <c r="BE3" t="n">
+        <v>61.51</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1229,6 +1240,9 @@
       <c r="BD4" t="n">
         <v>35.93</v>
       </c>
+      <c r="BE4" t="n">
+        <v>35.93</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1401,6 +1415,9 @@
       <c r="BD5" t="n">
         <v>49.37</v>
       </c>
+      <c r="BE5" t="n">
+        <v>49.37</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1573,6 +1590,9 @@
       <c r="BD6" t="n">
         <v>41.68</v>
       </c>
+      <c r="BE6" t="n">
+        <v>41.68</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1745,6 +1765,9 @@
       <c r="BD7" t="n">
         <v>62.45</v>
       </c>
+      <c r="BE7" t="n">
+        <v>62.45</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1917,6 +1940,9 @@
       <c r="BD8" t="n">
         <v>55.06</v>
       </c>
+      <c r="BE8" t="n">
+        <v>55.06</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2089,6 +2115,9 @@
       <c r="BD9" t="n">
         <v>64.84</v>
       </c>
+      <c r="BE9" t="n">
+        <v>62.59</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2261,6 +2290,9 @@
       <c r="BD10" t="n">
         <v>56.07</v>
       </c>
+      <c r="BE10" t="n">
+        <v>56.38</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2433,6 +2465,9 @@
       <c r="BD11" t="n">
         <v>58.06</v>
       </c>
+      <c r="BE11" t="n">
+        <v>60.31</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2605,6 +2640,9 @@
       <c r="BD12" t="n">
         <v>46.7</v>
       </c>
+      <c r="BE12" t="n">
+        <v>46.39</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2777,6 +2815,9 @@
       <c r="BD13" t="n">
         <v>62.5</v>
       </c>
+      <c r="BE13" t="n">
+        <v>62.5</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2949,6 +2990,9 @@
       <c r="BD14" t="n">
         <v>64.14</v>
       </c>
+      <c r="BE14" t="n">
+        <v>65.59999999999999</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -3121,6 +3165,9 @@
       <c r="BD15" t="n">
         <v>49.59</v>
       </c>
+      <c r="BE15" t="n">
+        <v>49.59</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -3293,6 +3340,9 @@
       <c r="BD16" t="n">
         <v>47.84</v>
       </c>
+      <c r="BE16" t="n">
+        <v>47.84</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -3465,6 +3515,9 @@
       <c r="BD17" t="n">
         <v>39.83</v>
       </c>
+      <c r="BE17" t="n">
+        <v>39.83</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -3637,6 +3690,9 @@
       <c r="BD18" t="n">
         <v>42.1</v>
       </c>
+      <c r="BE18" t="n">
+        <v>42.1</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -3809,6 +3865,9 @@
       <c r="BD19" t="n">
         <v>34.94</v>
       </c>
+      <c r="BE19" t="n">
+        <v>34.94</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -3981,6 +4040,9 @@
       <c r="BD20" t="n">
         <v>38.28</v>
       </c>
+      <c r="BE20" t="n">
+        <v>38.28</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -4153,6 +4215,9 @@
       <c r="BD21" t="n">
         <v>61.4</v>
       </c>
+      <c r="BE21" t="n">
+        <v>61.4</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -4325,6 +4390,9 @@
       <c r="BD22" t="n">
         <v>59.58</v>
       </c>
+      <c r="BE22" t="n">
+        <v>60.81</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -4497,6 +4565,9 @@
       <c r="BD23" t="n">
         <v>60.01</v>
       </c>
+      <c r="BE23" t="n">
+        <v>58.78</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -4669,6 +4740,9 @@
       <c r="BD24" t="n">
         <v>58.11</v>
       </c>
+      <c r="BE24" t="n">
+        <v>58.85</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -4841,6 +4915,9 @@
       <c r="BD25" t="n">
         <v>36.32</v>
       </c>
+      <c r="BE25" t="n">
+        <v>36.32</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -5013,6 +5090,9 @@
       <c r="BD26" t="n">
         <v>48.64</v>
       </c>
+      <c r="BE26" t="n">
+        <v>46.87</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -5185,6 +5265,9 @@
       <c r="BD27" t="n">
         <v>57.11</v>
       </c>
+      <c r="BE27" t="n">
+        <v>57.11</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -5357,6 +5440,9 @@
       <c r="BD28" t="n">
         <v>40.98</v>
       </c>
+      <c r="BE28" t="n">
+        <v>40.98</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -5529,6 +5615,9 @@
       <c r="BD29" t="n">
         <v>38.55</v>
       </c>
+      <c r="BE29" t="n">
+        <v>38.55</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -5701,6 +5790,9 @@
       <c r="BD30" t="n">
         <v>60.71</v>
       </c>
+      <c r="BE30" t="n">
+        <v>60.71</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -5873,6 +5965,9 @@
       <c r="BD31" t="n">
         <v>26.93</v>
       </c>
+      <c r="BE31" t="n">
+        <v>26.93</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -6045,6 +6140,9 @@
       <c r="BD32" t="n">
         <v>55.28</v>
       </c>
+      <c r="BE32" t="n">
+        <v>54.54</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -6217,6 +6315,9 @@
       <c r="BD33" t="n">
         <v>46.27</v>
       </c>
+      <c r="BE33" t="n">
+        <v>46.27</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -6388,6 +6489,9 @@
       </c>
       <c r="BD34" t="n">
         <v>47.04</v>
+      </c>
+      <c r="BE34" t="n">
+        <v>48.81</v>
       </c>
     </row>
   </sheetData>

--- a/gaa_rankings_pivot.xlsx
+++ b/gaa_rankings_pivot.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BE34"/>
+  <dimension ref="A1:BF34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -718,6 +718,11 @@
           <t>2026-06-22</t>
         </is>
       </c>
+      <c r="BF1" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -893,6 +898,9 @@
       <c r="BE2" t="n">
         <v>40.72</v>
       </c>
+      <c r="BF2" t="n">
+        <v>40.72</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1068,6 +1076,9 @@
       <c r="BE3" t="n">
         <v>61.51</v>
       </c>
+      <c r="BF3" t="n">
+        <v>61.51</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1243,6 +1254,9 @@
       <c r="BE4" t="n">
         <v>35.93</v>
       </c>
+      <c r="BF4" t="n">
+        <v>35.93</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1418,6 +1432,9 @@
       <c r="BE5" t="n">
         <v>49.37</v>
       </c>
+      <c r="BF5" t="n">
+        <v>49.37</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1593,6 +1610,9 @@
       <c r="BE6" t="n">
         <v>41.68</v>
       </c>
+      <c r="BF6" t="n">
+        <v>41.68</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1768,6 +1788,9 @@
       <c r="BE7" t="n">
         <v>62.45</v>
       </c>
+      <c r="BF7" t="n">
+        <v>62.45</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1943,6 +1966,9 @@
       <c r="BE8" t="n">
         <v>55.06</v>
       </c>
+      <c r="BF8" t="n">
+        <v>55.06</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2118,6 +2144,9 @@
       <c r="BE9" t="n">
         <v>62.59</v>
       </c>
+      <c r="BF9" t="n">
+        <v>62.59</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2293,6 +2322,9 @@
       <c r="BE10" t="n">
         <v>56.38</v>
       </c>
+      <c r="BF10" t="n">
+        <v>56.38</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2468,6 +2500,9 @@
       <c r="BE11" t="n">
         <v>60.31</v>
       </c>
+      <c r="BF11" t="n">
+        <v>60.31</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2643,6 +2678,9 @@
       <c r="BE12" t="n">
         <v>46.39</v>
       </c>
+      <c r="BF12" t="n">
+        <v>46.39</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2818,6 +2856,9 @@
       <c r="BE13" t="n">
         <v>62.5</v>
       </c>
+      <c r="BF13" t="n">
+        <v>62.5</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2993,6 +3034,9 @@
       <c r="BE14" t="n">
         <v>65.59999999999999</v>
       </c>
+      <c r="BF14" t="n">
+        <v>65.59999999999999</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -3168,6 +3212,9 @@
       <c r="BE15" t="n">
         <v>49.59</v>
       </c>
+      <c r="BF15" t="n">
+        <v>49.59</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -3343,6 +3390,9 @@
       <c r="BE16" t="n">
         <v>47.84</v>
       </c>
+      <c r="BF16" t="n">
+        <v>47.84</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -3518,6 +3568,9 @@
       <c r="BE17" t="n">
         <v>39.83</v>
       </c>
+      <c r="BF17" t="n">
+        <v>39.83</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -3693,6 +3746,9 @@
       <c r="BE18" t="n">
         <v>42.1</v>
       </c>
+      <c r="BF18" t="n">
+        <v>42.1</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -3868,6 +3924,9 @@
       <c r="BE19" t="n">
         <v>34.94</v>
       </c>
+      <c r="BF19" t="n">
+        <v>34.94</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -4043,6 +4102,9 @@
       <c r="BE20" t="n">
         <v>38.28</v>
       </c>
+      <c r="BF20" t="n">
+        <v>38.28</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -4218,6 +4280,9 @@
       <c r="BE21" t="n">
         <v>61.4</v>
       </c>
+      <c r="BF21" t="n">
+        <v>61.4</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -4393,6 +4458,9 @@
       <c r="BE22" t="n">
         <v>60.81</v>
       </c>
+      <c r="BF22" t="n">
+        <v>60.81</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -4568,6 +4636,9 @@
       <c r="BE23" t="n">
         <v>58.78</v>
       </c>
+      <c r="BF23" t="n">
+        <v>58.78</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -4743,6 +4814,9 @@
       <c r="BE24" t="n">
         <v>58.85</v>
       </c>
+      <c r="BF24" t="n">
+        <v>59.42</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -4918,6 +4992,9 @@
       <c r="BE25" t="n">
         <v>36.32</v>
       </c>
+      <c r="BF25" t="n">
+        <v>36.32</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -5093,6 +5170,9 @@
       <c r="BE26" t="n">
         <v>46.87</v>
       </c>
+      <c r="BF26" t="n">
+        <v>46.87</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -5268,6 +5348,9 @@
       <c r="BE27" t="n">
         <v>57.11</v>
       </c>
+      <c r="BF27" t="n">
+        <v>57.11</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -5443,6 +5526,9 @@
       <c r="BE28" t="n">
         <v>40.98</v>
       </c>
+      <c r="BF28" t="n">
+        <v>40.98</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -5618,6 +5704,9 @@
       <c r="BE29" t="n">
         <v>38.55</v>
       </c>
+      <c r="BF29" t="n">
+        <v>38.55</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -5793,6 +5882,9 @@
       <c r="BE30" t="n">
         <v>60.71</v>
       </c>
+      <c r="BF30" t="n">
+        <v>60.71</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -5968,6 +6060,9 @@
       <c r="BE31" t="n">
         <v>26.93</v>
       </c>
+      <c r="BF31" t="n">
+        <v>26.93</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -6143,6 +6238,9 @@
       <c r="BE32" t="n">
         <v>54.54</v>
       </c>
+      <c r="BF32" t="n">
+        <v>53.97</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -6318,6 +6416,9 @@
       <c r="BE33" t="n">
         <v>46.27</v>
       </c>
+      <c r="BF33" t="n">
+        <v>46.27</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -6491,6 +6592,9 @@
         <v>47.04</v>
       </c>
       <c r="BE34" t="n">
+        <v>48.81</v>
+      </c>
+      <c r="BF34" t="n">
         <v>48.81</v>
       </c>
     </row>

--- a/gaa_rankings_pivot.xlsx
+++ b/gaa_rankings_pivot.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BF34"/>
+  <dimension ref="A1:BG34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -723,6 +723,11 @@
           <t>2026-06-23</t>
         </is>
       </c>
+      <c r="BG1" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -901,6 +906,9 @@
       <c r="BF2" t="n">
         <v>40.72</v>
       </c>
+      <c r="BG2" t="n">
+        <v>40.72</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1079,6 +1087,9 @@
       <c r="BF3" t="n">
         <v>61.51</v>
       </c>
+      <c r="BG3" t="n">
+        <v>61.51</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1257,6 +1268,9 @@
       <c r="BF4" t="n">
         <v>35.93</v>
       </c>
+      <c r="BG4" t="n">
+        <v>35.93</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1435,6 +1449,9 @@
       <c r="BF5" t="n">
         <v>49.37</v>
       </c>
+      <c r="BG5" t="n">
+        <v>49.37</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1613,6 +1630,9 @@
       <c r="BF6" t="n">
         <v>41.68</v>
       </c>
+      <c r="BG6" t="n">
+        <v>41.68</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1791,6 +1811,9 @@
       <c r="BF7" t="n">
         <v>62.45</v>
       </c>
+      <c r="BG7" t="n">
+        <v>60.67</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1969,6 +1992,9 @@
       <c r="BF8" t="n">
         <v>55.06</v>
       </c>
+      <c r="BG8" t="n">
+        <v>55.06</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2147,6 +2173,9 @@
       <c r="BF9" t="n">
         <v>62.59</v>
       </c>
+      <c r="BG9" t="n">
+        <v>62.59</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2325,6 +2354,9 @@
       <c r="BF10" t="n">
         <v>56.38</v>
       </c>
+      <c r="BG10" t="n">
+        <v>56.38</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2503,6 +2535,9 @@
       <c r="BF11" t="n">
         <v>60.31</v>
       </c>
+      <c r="BG11" t="n">
+        <v>61.84</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2681,6 +2716,9 @@
       <c r="BF12" t="n">
         <v>46.39</v>
       </c>
+      <c r="BG12" t="n">
+        <v>46.39</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2859,6 +2897,9 @@
       <c r="BF13" t="n">
         <v>62.5</v>
       </c>
+      <c r="BG13" t="n">
+        <v>60.97</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -3037,6 +3078,9 @@
       <c r="BF14" t="n">
         <v>65.59999999999999</v>
       </c>
+      <c r="BG14" t="n">
+        <v>66.33</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -3215,6 +3259,9 @@
       <c r="BF15" t="n">
         <v>49.59</v>
       </c>
+      <c r="BG15" t="n">
+        <v>49.59</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -3393,6 +3440,9 @@
       <c r="BF16" t="n">
         <v>47.84</v>
       </c>
+      <c r="BG16" t="n">
+        <v>47.84</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -3571,6 +3621,9 @@
       <c r="BF17" t="n">
         <v>39.83</v>
       </c>
+      <c r="BG17" t="n">
+        <v>39.83</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -3749,6 +3802,9 @@
       <c r="BF18" t="n">
         <v>42.1</v>
       </c>
+      <c r="BG18" t="n">
+        <v>42.1</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -3927,6 +3983,9 @@
       <c r="BF19" t="n">
         <v>34.94</v>
       </c>
+      <c r="BG19" t="n">
+        <v>34.94</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -4105,6 +4164,9 @@
       <c r="BF20" t="n">
         <v>38.28</v>
       </c>
+      <c r="BG20" t="n">
+        <v>38.28</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -4283,6 +4345,9 @@
       <c r="BF21" t="n">
         <v>61.4</v>
       </c>
+      <c r="BG21" t="n">
+        <v>62.56</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -4461,6 +4526,9 @@
       <c r="BF22" t="n">
         <v>60.81</v>
       </c>
+      <c r="BG22" t="n">
+        <v>62.59</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -4639,6 +4707,9 @@
       <c r="BF23" t="n">
         <v>58.78</v>
       </c>
+      <c r="BG23" t="n">
+        <v>58.78</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -4817,6 +4888,9 @@
       <c r="BF24" t="n">
         <v>59.42</v>
       </c>
+      <c r="BG24" t="n">
+        <v>58.26</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -4995,6 +5069,9 @@
       <c r="BF25" t="n">
         <v>36.32</v>
       </c>
+      <c r="BG25" t="n">
+        <v>36.32</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -5173,6 +5250,9 @@
       <c r="BF26" t="n">
         <v>46.87</v>
       </c>
+      <c r="BG26" t="n">
+        <v>46.87</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -5351,6 +5431,9 @@
       <c r="BF27" t="n">
         <v>57.11</v>
       </c>
+      <c r="BG27" t="n">
+        <v>57.11</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -5529,6 +5612,9 @@
       <c r="BF28" t="n">
         <v>40.98</v>
       </c>
+      <c r="BG28" t="n">
+        <v>40.98</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -5707,6 +5793,9 @@
       <c r="BF29" t="n">
         <v>38.55</v>
       </c>
+      <c r="BG29" t="n">
+        <v>38.55</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -5885,6 +5974,9 @@
       <c r="BF30" t="n">
         <v>60.71</v>
       </c>
+      <c r="BG30" t="n">
+        <v>59.98</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -6063,6 +6155,9 @@
       <c r="BF31" t="n">
         <v>26.93</v>
       </c>
+      <c r="BG31" t="n">
+        <v>26.93</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -6241,6 +6336,9 @@
       <c r="BF32" t="n">
         <v>53.97</v>
       </c>
+      <c r="BG32" t="n">
+        <v>53.97</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -6419,6 +6517,9 @@
       <c r="BF33" t="n">
         <v>46.27</v>
       </c>
+      <c r="BG33" t="n">
+        <v>46.27</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -6595,6 +6696,9 @@
         <v>48.81</v>
       </c>
       <c r="BF34" t="n">
+        <v>48.81</v>
+      </c>
+      <c r="BG34" t="n">
         <v>48.81</v>
       </c>
     </row>

--- a/gaa_rankings_pivot.xlsx
+++ b/gaa_rankings_pivot.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BG34"/>
+  <dimension ref="A1:BH34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -728,6 +728,11 @@
           <t>2026-06-30</t>
         </is>
       </c>
+      <c r="BH1" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -909,6 +914,9 @@
       <c r="BG2" t="n">
         <v>40.72</v>
       </c>
+      <c r="BH2" t="n">
+        <v>40.72</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1090,6 +1098,9 @@
       <c r="BG3" t="n">
         <v>61.51</v>
       </c>
+      <c r="BH3" t="n">
+        <v>61.51</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1271,6 +1282,9 @@
       <c r="BG4" t="n">
         <v>35.93</v>
       </c>
+      <c r="BH4" t="n">
+        <v>35.93</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1452,6 +1466,9 @@
       <c r="BG5" t="n">
         <v>49.37</v>
       </c>
+      <c r="BH5" t="n">
+        <v>49.37</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1633,6 +1650,9 @@
       <c r="BG6" t="n">
         <v>41.68</v>
       </c>
+      <c r="BH6" t="n">
+        <v>41.68</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1814,6 +1834,9 @@
       <c r="BG7" t="n">
         <v>60.67</v>
       </c>
+      <c r="BH7" t="n">
+        <v>60.67</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1995,6 +2018,9 @@
       <c r="BG8" t="n">
         <v>55.06</v>
       </c>
+      <c r="BH8" t="n">
+        <v>55.06</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2176,6 +2202,9 @@
       <c r="BG9" t="n">
         <v>62.59</v>
       </c>
+      <c r="BH9" t="n">
+        <v>62.59</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2357,6 +2386,9 @@
       <c r="BG10" t="n">
         <v>56.38</v>
       </c>
+      <c r="BH10" t="n">
+        <v>56.38</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2538,6 +2570,9 @@
       <c r="BG11" t="n">
         <v>61.84</v>
       </c>
+      <c r="BH11" t="n">
+        <v>61.84</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2719,6 +2754,9 @@
       <c r="BG12" t="n">
         <v>46.39</v>
       </c>
+      <c r="BH12" t="n">
+        <v>46.39</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2900,6 +2938,9 @@
       <c r="BG13" t="n">
         <v>60.97</v>
       </c>
+      <c r="BH13" t="n">
+        <v>60.97</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -3081,6 +3122,9 @@
       <c r="BG14" t="n">
         <v>66.33</v>
       </c>
+      <c r="BH14" t="n">
+        <v>66.33</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -3262,6 +3306,9 @@
       <c r="BG15" t="n">
         <v>49.59</v>
       </c>
+      <c r="BH15" t="n">
+        <v>49.59</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -3443,6 +3490,9 @@
       <c r="BG16" t="n">
         <v>47.84</v>
       </c>
+      <c r="BH16" t="n">
+        <v>47.84</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -3624,6 +3674,9 @@
       <c r="BG17" t="n">
         <v>39.83</v>
       </c>
+      <c r="BH17" t="n">
+        <v>39.83</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -3805,6 +3858,9 @@
       <c r="BG18" t="n">
         <v>42.1</v>
       </c>
+      <c r="BH18" t="n">
+        <v>42.1</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -3986,6 +4042,9 @@
       <c r="BG19" t="n">
         <v>34.94</v>
       </c>
+      <c r="BH19" t="n">
+        <v>34.94</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -4167,6 +4226,9 @@
       <c r="BG20" t="n">
         <v>38.28</v>
       </c>
+      <c r="BH20" t="n">
+        <v>38.28</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -4348,6 +4410,9 @@
       <c r="BG21" t="n">
         <v>62.56</v>
       </c>
+      <c r="BH21" t="n">
+        <v>62.56</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -4529,6 +4594,9 @@
       <c r="BG22" t="n">
         <v>62.59</v>
       </c>
+      <c r="BH22" t="n">
+        <v>62.59</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -4710,6 +4778,9 @@
       <c r="BG23" t="n">
         <v>58.78</v>
       </c>
+      <c r="BH23" t="n">
+        <v>58.78</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -4891,6 +4962,9 @@
       <c r="BG24" t="n">
         <v>58.26</v>
       </c>
+      <c r="BH24" t="n">
+        <v>58.26</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -5072,6 +5146,9 @@
       <c r="BG25" t="n">
         <v>36.32</v>
       </c>
+      <c r="BH25" t="n">
+        <v>36.32</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -5253,6 +5330,9 @@
       <c r="BG26" t="n">
         <v>46.87</v>
       </c>
+      <c r="BH26" t="n">
+        <v>46.87</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -5434,6 +5514,9 @@
       <c r="BG27" t="n">
         <v>57.11</v>
       </c>
+      <c r="BH27" t="n">
+        <v>57.11</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -5615,6 +5698,9 @@
       <c r="BG28" t="n">
         <v>40.98</v>
       </c>
+      <c r="BH28" t="n">
+        <v>40.98</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -5796,6 +5882,9 @@
       <c r="BG29" t="n">
         <v>38.55</v>
       </c>
+      <c r="BH29" t="n">
+        <v>38.55</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -5977,6 +6066,9 @@
       <c r="BG30" t="n">
         <v>59.98</v>
       </c>
+      <c r="BH30" t="n">
+        <v>59.98</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -6158,6 +6250,9 @@
       <c r="BG31" t="n">
         <v>26.93</v>
       </c>
+      <c r="BH31" t="n">
+        <v>26.93</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -6339,6 +6434,9 @@
       <c r="BG32" t="n">
         <v>53.97</v>
       </c>
+      <c r="BH32" t="n">
+        <v>53.97</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -6520,6 +6618,9 @@
       <c r="BG33" t="n">
         <v>46.27</v>
       </c>
+      <c r="BH33" t="n">
+        <v>46.27</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -6699,6 +6800,9 @@
         <v>48.81</v>
       </c>
       <c r="BG34" t="n">
+        <v>48.81</v>
+      </c>
+      <c r="BH34" t="n">
         <v>48.81</v>
       </c>
     </row>

--- a/gaa_rankings_pivot.xlsx
+++ b/gaa_rankings_pivot.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH34"/>
+  <dimension ref="A1:BI34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -733,6 +733,11 @@
           <t>2026-07-07</t>
         </is>
       </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -917,6 +922,9 @@
       <c r="BH2" t="n">
         <v>40.72</v>
       </c>
+      <c r="BI2" t="n">
+        <v>40.72</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1101,6 +1109,9 @@
       <c r="BH3" t="n">
         <v>61.51</v>
       </c>
+      <c r="BI3" t="n">
+        <v>61.51</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1285,6 +1296,9 @@
       <c r="BH4" t="n">
         <v>35.93</v>
       </c>
+      <c r="BI4" t="n">
+        <v>35.93</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1469,6 +1483,9 @@
       <c r="BH5" t="n">
         <v>49.37</v>
       </c>
+      <c r="BI5" t="n">
+        <v>49.37</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1653,6 +1670,9 @@
       <c r="BH6" t="n">
         <v>41.68</v>
       </c>
+      <c r="BI6" t="n">
+        <v>41.68</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1837,6 +1857,9 @@
       <c r="BH7" t="n">
         <v>60.67</v>
       </c>
+      <c r="BI7" t="n">
+        <v>60.67</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2021,6 +2044,9 @@
       <c r="BH8" t="n">
         <v>55.06</v>
       </c>
+      <c r="BI8" t="n">
+        <v>55.06</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2205,6 +2231,9 @@
       <c r="BH9" t="n">
         <v>62.59</v>
       </c>
+      <c r="BI9" t="n">
+        <v>62.59</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2389,6 +2418,9 @@
       <c r="BH10" t="n">
         <v>56.38</v>
       </c>
+      <c r="BI10" t="n">
+        <v>53.83</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2573,6 +2605,9 @@
       <c r="BH11" t="n">
         <v>61.84</v>
       </c>
+      <c r="BI11" t="n">
+        <v>60.76</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2757,6 +2792,9 @@
       <c r="BH12" t="n">
         <v>46.39</v>
       </c>
+      <c r="BI12" t="n">
+        <v>46.39</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2941,6 +2979,9 @@
       <c r="BH13" t="n">
         <v>60.97</v>
       </c>
+      <c r="BI13" t="n">
+        <v>60.97</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -3125,6 +3166,9 @@
       <c r="BH14" t="n">
         <v>66.33</v>
       </c>
+      <c r="BI14" t="n">
+        <v>67.41</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -3309,6 +3353,9 @@
       <c r="BH15" t="n">
         <v>49.59</v>
       </c>
+      <c r="BI15" t="n">
+        <v>49.59</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -3493,6 +3540,9 @@
       <c r="BH16" t="n">
         <v>47.84</v>
       </c>
+      <c r="BI16" t="n">
+        <v>47.84</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -3677,6 +3727,9 @@
       <c r="BH17" t="n">
         <v>39.83</v>
       </c>
+      <c r="BI17" t="n">
+        <v>39.83</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -3861,6 +3914,9 @@
       <c r="BH18" t="n">
         <v>42.1</v>
       </c>
+      <c r="BI18" t="n">
+        <v>42.1</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -4045,6 +4101,9 @@
       <c r="BH19" t="n">
         <v>34.94</v>
       </c>
+      <c r="BI19" t="n">
+        <v>34.94</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -4229,6 +4288,9 @@
       <c r="BH20" t="n">
         <v>38.28</v>
       </c>
+      <c r="BI20" t="n">
+        <v>38.28</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -4413,6 +4475,9 @@
       <c r="BH21" t="n">
         <v>62.56</v>
       </c>
+      <c r="BI21" t="n">
+        <v>60.32</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -4597,6 +4662,9 @@
       <c r="BH22" t="n">
         <v>62.59</v>
       </c>
+      <c r="BI22" t="n">
+        <v>64.83</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -4781,6 +4849,9 @@
       <c r="BH23" t="n">
         <v>58.78</v>
       </c>
+      <c r="BI23" t="n">
+        <v>58.78</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -4965,6 +5036,9 @@
       <c r="BH24" t="n">
         <v>58.26</v>
       </c>
+      <c r="BI24" t="n">
+        <v>58.26</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -5149,6 +5223,9 @@
       <c r="BH25" t="n">
         <v>36.32</v>
       </c>
+      <c r="BI25" t="n">
+        <v>36.32</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -5333,6 +5410,9 @@
       <c r="BH26" t="n">
         <v>46.87</v>
       </c>
+      <c r="BI26" t="n">
+        <v>46.87</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -5517,6 +5597,9 @@
       <c r="BH27" t="n">
         <v>57.11</v>
       </c>
+      <c r="BI27" t="n">
+        <v>57.11</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -5701,6 +5784,9 @@
       <c r="BH28" t="n">
         <v>40.98</v>
       </c>
+      <c r="BI28" t="n">
+        <v>40.98</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -5885,6 +5971,9 @@
       <c r="BH29" t="n">
         <v>38.55</v>
       </c>
+      <c r="BI29" t="n">
+        <v>38.55</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -6069,6 +6158,9 @@
       <c r="BH30" t="n">
         <v>59.98</v>
       </c>
+      <c r="BI30" t="n">
+        <v>59.98</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -6253,6 +6345,9 @@
       <c r="BH31" t="n">
         <v>26.93</v>
       </c>
+      <c r="BI31" t="n">
+        <v>26.93</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -6437,6 +6532,9 @@
       <c r="BH32" t="n">
         <v>53.97</v>
       </c>
+      <c r="BI32" t="n">
+        <v>53.97</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -6621,6 +6719,9 @@
       <c r="BH33" t="n">
         <v>46.27</v>
       </c>
+      <c r="BI33" t="n">
+        <v>46.27</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -6804,6 +6905,9 @@
       </c>
       <c r="BH34" t="n">
         <v>48.81</v>
+      </c>
+      <c r="BI34" t="n">
+        <v>51.36</v>
       </c>
     </row>
   </sheetData>

--- a/gaa_rankings_pivot.xlsx
+++ b/gaa_rankings_pivot.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI34"/>
+  <dimension ref="A1:BJ34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -738,6 +738,11 @@
           <t>2026-07-14</t>
         </is>
       </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -925,6 +930,9 @@
       <c r="BI2" t="n">
         <v>40.72</v>
       </c>
+      <c r="BJ2" t="n">
+        <v>40.72</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1112,6 +1120,9 @@
       <c r="BI3" t="n">
         <v>61.51</v>
       </c>
+      <c r="BJ3" t="n">
+        <v>61.51</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1299,6 +1310,9 @@
       <c r="BI4" t="n">
         <v>35.93</v>
       </c>
+      <c r="BJ4" t="n">
+        <v>35.93</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1486,6 +1500,9 @@
       <c r="BI5" t="n">
         <v>49.37</v>
       </c>
+      <c r="BJ5" t="n">
+        <v>49.37</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1673,6 +1690,9 @@
       <c r="BI6" t="n">
         <v>41.68</v>
       </c>
+      <c r="BJ6" t="n">
+        <v>41.68</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1860,6 +1880,9 @@
       <c r="BI7" t="n">
         <v>60.67</v>
       </c>
+      <c r="BJ7" t="n">
+        <v>60.67</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2047,6 +2070,9 @@
       <c r="BI8" t="n">
         <v>55.06</v>
       </c>
+      <c r="BJ8" t="n">
+        <v>55.06</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2234,6 +2260,9 @@
       <c r="BI9" t="n">
         <v>62.59</v>
       </c>
+      <c r="BJ9" t="n">
+        <v>62.59</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2421,6 +2450,9 @@
       <c r="BI10" t="n">
         <v>53.83</v>
       </c>
+      <c r="BJ10" t="n">
+        <v>53.83</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2608,6 +2640,9 @@
       <c r="BI11" t="n">
         <v>60.76</v>
       </c>
+      <c r="BJ11" t="n">
+        <v>60.76</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2795,6 +2830,9 @@
       <c r="BI12" t="n">
         <v>46.39</v>
       </c>
+      <c r="BJ12" t="n">
+        <v>46.39</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2982,6 +3020,9 @@
       <c r="BI13" t="n">
         <v>60.97</v>
       </c>
+      <c r="BJ13" t="n">
+        <v>60.97</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -3169,6 +3210,9 @@
       <c r="BI14" t="n">
         <v>67.41</v>
       </c>
+      <c r="BJ14" t="n">
+        <v>67.41</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -3356,6 +3400,9 @@
       <c r="BI15" t="n">
         <v>49.59</v>
       </c>
+      <c r="BJ15" t="n">
+        <v>49.59</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -3543,6 +3590,9 @@
       <c r="BI16" t="n">
         <v>47.84</v>
       </c>
+      <c r="BJ16" t="n">
+        <v>47.84</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -3730,6 +3780,9 @@
       <c r="BI17" t="n">
         <v>39.83</v>
       </c>
+      <c r="BJ17" t="n">
+        <v>39.83</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -3917,6 +3970,9 @@
       <c r="BI18" t="n">
         <v>42.1</v>
       </c>
+      <c r="BJ18" t="n">
+        <v>42.1</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -4104,6 +4160,9 @@
       <c r="BI19" t="n">
         <v>34.94</v>
       </c>
+      <c r="BJ19" t="n">
+        <v>34.94</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -4291,6 +4350,9 @@
       <c r="BI20" t="n">
         <v>38.28</v>
       </c>
+      <c r="BJ20" t="n">
+        <v>38.28</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -4478,6 +4540,9 @@
       <c r="BI21" t="n">
         <v>60.32</v>
       </c>
+      <c r="BJ21" t="n">
+        <v>60.32</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -4665,6 +4730,9 @@
       <c r="BI22" t="n">
         <v>64.83</v>
       </c>
+      <c r="BJ22" t="n">
+        <v>64.83</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -4852,6 +4920,9 @@
       <c r="BI23" t="n">
         <v>58.78</v>
       </c>
+      <c r="BJ23" t="n">
+        <v>58.78</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -5039,6 +5110,9 @@
       <c r="BI24" t="n">
         <v>58.26</v>
       </c>
+      <c r="BJ24" t="n">
+        <v>58.26</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -5226,6 +5300,9 @@
       <c r="BI25" t="n">
         <v>36.32</v>
       </c>
+      <c r="BJ25" t="n">
+        <v>36.32</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -5413,6 +5490,9 @@
       <c r="BI26" t="n">
         <v>46.87</v>
       </c>
+      <c r="BJ26" t="n">
+        <v>46.87</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -5600,6 +5680,9 @@
       <c r="BI27" t="n">
         <v>57.11</v>
       </c>
+      <c r="BJ27" t="n">
+        <v>57.11</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -5787,6 +5870,9 @@
       <c r="BI28" t="n">
         <v>40.98</v>
       </c>
+      <c r="BJ28" t="n">
+        <v>40.98</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -5974,6 +6060,9 @@
       <c r="BI29" t="n">
         <v>38.55</v>
       </c>
+      <c r="BJ29" t="n">
+        <v>38.55</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -6161,6 +6250,9 @@
       <c r="BI30" t="n">
         <v>59.98</v>
       </c>
+      <c r="BJ30" t="n">
+        <v>59.98</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -6348,6 +6440,9 @@
       <c r="BI31" t="n">
         <v>26.93</v>
       </c>
+      <c r="BJ31" t="n">
+        <v>26.93</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -6535,6 +6630,9 @@
       <c r="BI32" t="n">
         <v>53.97</v>
       </c>
+      <c r="BJ32" t="n">
+        <v>53.97</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -6722,6 +6820,9 @@
       <c r="BI33" t="n">
         <v>46.27</v>
       </c>
+      <c r="BJ33" t="n">
+        <v>46.27</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -6907,6 +7008,9 @@
         <v>48.81</v>
       </c>
       <c r="BI34" t="n">
+        <v>51.36</v>
+      </c>
+      <c r="BJ34" t="n">
         <v>51.36</v>
       </c>
     </row>

--- a/gaa_rankings_pivot.xlsx
+++ b/gaa_rankings_pivot.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BJ34"/>
+  <dimension ref="A1:BK34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -743,6 +743,11 @@
           <t>2026-07-21</t>
         </is>
       </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -933,6 +938,9 @@
       <c r="BJ2" t="n">
         <v>40.72</v>
       </c>
+      <c r="BK2" t="n">
+        <v>40.72</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1123,6 +1131,9 @@
       <c r="BJ3" t="n">
         <v>61.51</v>
       </c>
+      <c r="BK3" t="n">
+        <v>61.51</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1313,6 +1324,9 @@
       <c r="BJ4" t="n">
         <v>35.93</v>
       </c>
+      <c r="BK4" t="n">
+        <v>35.93</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1503,6 +1517,9 @@
       <c r="BJ5" t="n">
         <v>49.37</v>
       </c>
+      <c r="BK5" t="n">
+        <v>49.37</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1693,6 +1710,9 @@
       <c r="BJ6" t="n">
         <v>41.68</v>
       </c>
+      <c r="BK6" t="n">
+        <v>41.68</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1883,6 +1903,9 @@
       <c r="BJ7" t="n">
         <v>60.67</v>
       </c>
+      <c r="BK7" t="n">
+        <v>60.67</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2073,6 +2096,9 @@
       <c r="BJ8" t="n">
         <v>55.06</v>
       </c>
+      <c r="BK8" t="n">
+        <v>55.06</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2263,6 +2289,9 @@
       <c r="BJ9" t="n">
         <v>62.59</v>
       </c>
+      <c r="BK9" t="n">
+        <v>62.59</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2453,6 +2482,9 @@
       <c r="BJ10" t="n">
         <v>53.83</v>
       </c>
+      <c r="BK10" t="n">
+        <v>53.83</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2643,6 +2675,9 @@
       <c r="BJ11" t="n">
         <v>60.76</v>
       </c>
+      <c r="BK11" t="n">
+        <v>60.76</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2833,6 +2868,9 @@
       <c r="BJ12" t="n">
         <v>46.39</v>
       </c>
+      <c r="BK12" t="n">
+        <v>46.39</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -3023,6 +3061,9 @@
       <c r="BJ13" t="n">
         <v>60.97</v>
       </c>
+      <c r="BK13" t="n">
+        <v>60.97</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -3213,6 +3254,9 @@
       <c r="BJ14" t="n">
         <v>67.41</v>
       </c>
+      <c r="BK14" t="n">
+        <v>65.48</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -3403,6 +3447,9 @@
       <c r="BJ15" t="n">
         <v>49.59</v>
       </c>
+      <c r="BK15" t="n">
+        <v>49.59</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -3593,6 +3640,9 @@
       <c r="BJ16" t="n">
         <v>47.84</v>
       </c>
+      <c r="BK16" t="n">
+        <v>47.84</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -3783,6 +3833,9 @@
       <c r="BJ17" t="n">
         <v>39.83</v>
       </c>
+      <c r="BK17" t="n">
+        <v>39.83</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -3973,6 +4026,9 @@
       <c r="BJ18" t="n">
         <v>42.1</v>
       </c>
+      <c r="BK18" t="n">
+        <v>42.1</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -4163,6 +4219,9 @@
       <c r="BJ19" t="n">
         <v>34.94</v>
       </c>
+      <c r="BK19" t="n">
+        <v>34.94</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -4353,6 +4412,9 @@
       <c r="BJ20" t="n">
         <v>38.28</v>
       </c>
+      <c r="BK20" t="n">
+        <v>38.28</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -4543,6 +4605,9 @@
       <c r="BJ21" t="n">
         <v>60.32</v>
       </c>
+      <c r="BK21" t="n">
+        <v>60.32</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -4733,6 +4798,9 @@
       <c r="BJ22" t="n">
         <v>64.83</v>
       </c>
+      <c r="BK22" t="n">
+        <v>66.76000000000001</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -4923,6 +4991,9 @@
       <c r="BJ23" t="n">
         <v>58.78</v>
       </c>
+      <c r="BK23" t="n">
+        <v>58.78</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -5113,6 +5184,9 @@
       <c r="BJ24" t="n">
         <v>58.26</v>
       </c>
+      <c r="BK24" t="n">
+        <v>58.26</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -5303,6 +5377,9 @@
       <c r="BJ25" t="n">
         <v>36.32</v>
       </c>
+      <c r="BK25" t="n">
+        <v>36.32</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -5493,6 +5570,9 @@
       <c r="BJ26" t="n">
         <v>46.87</v>
       </c>
+      <c r="BK26" t="n">
+        <v>46.87</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -5683,6 +5763,9 @@
       <c r="BJ27" t="n">
         <v>57.11</v>
       </c>
+      <c r="BK27" t="n">
+        <v>57.11</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -5873,6 +5956,9 @@
       <c r="BJ28" t="n">
         <v>40.98</v>
       </c>
+      <c r="BK28" t="n">
+        <v>40.98</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -6063,6 +6149,9 @@
       <c r="BJ29" t="n">
         <v>38.55</v>
       </c>
+      <c r="BK29" t="n">
+        <v>38.55</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -6253,6 +6342,9 @@
       <c r="BJ30" t="n">
         <v>59.98</v>
       </c>
+      <c r="BK30" t="n">
+        <v>59.98</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -6443,6 +6535,9 @@
       <c r="BJ31" t="n">
         <v>26.93</v>
       </c>
+      <c r="BK31" t="n">
+        <v>26.93</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -6633,6 +6728,9 @@
       <c r="BJ32" t="n">
         <v>53.97</v>
       </c>
+      <c r="BK32" t="n">
+        <v>53.97</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -6823,6 +6921,9 @@
       <c r="BJ33" t="n">
         <v>46.27</v>
       </c>
+      <c r="BK33" t="n">
+        <v>46.27</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -7011,6 +7112,9 @@
         <v>51.36</v>
       </c>
       <c r="BJ34" t="n">
+        <v>51.36</v>
+      </c>
+      <c r="BK34" t="n">
         <v>51.36</v>
       </c>
     </row>

--- a/gaa_rankings_pivot.xlsx
+++ b/gaa_rankings_pivot.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BK34"/>
+  <dimension ref="A1:BL34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -748,6 +748,11 @@
           <t>2026-07-28</t>
         </is>
       </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -941,6 +946,9 @@
       <c r="BK2" t="n">
         <v>40.72</v>
       </c>
+      <c r="BL2" t="n">
+        <v>40.72</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1134,6 +1142,9 @@
       <c r="BK3" t="n">
         <v>61.51</v>
       </c>
+      <c r="BL3" t="n">
+        <v>61.51</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1327,6 +1338,9 @@
       <c r="BK4" t="n">
         <v>35.93</v>
       </c>
+      <c r="BL4" t="n">
+        <v>35.93</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1520,6 +1534,9 @@
       <c r="BK5" t="n">
         <v>49.37</v>
       </c>
+      <c r="BL5" t="n">
+        <v>49.37</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1713,6 +1730,9 @@
       <c r="BK6" t="n">
         <v>41.68</v>
       </c>
+      <c r="BL6" t="n">
+        <v>41.68</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1906,6 +1926,9 @@
       <c r="BK7" t="n">
         <v>60.67</v>
       </c>
+      <c r="BL7" t="n">
+        <v>60.67</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2099,6 +2122,9 @@
       <c r="BK8" t="n">
         <v>55.06</v>
       </c>
+      <c r="BL8" t="n">
+        <v>55.06</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2292,6 +2318,9 @@
       <c r="BK9" t="n">
         <v>62.59</v>
       </c>
+      <c r="BL9" t="n">
+        <v>62.59</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2485,6 +2514,9 @@
       <c r="BK10" t="n">
         <v>53.83</v>
       </c>
+      <c r="BL10" t="n">
+        <v>53.83</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2678,6 +2710,9 @@
       <c r="BK11" t="n">
         <v>60.76</v>
       </c>
+      <c r="BL11" t="n">
+        <v>60.76</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2871,6 +2906,9 @@
       <c r="BK12" t="n">
         <v>46.39</v>
       </c>
+      <c r="BL12" t="n">
+        <v>46.39</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -3064,6 +3102,9 @@
       <c r="BK13" t="n">
         <v>60.97</v>
       </c>
+      <c r="BL13" t="n">
+        <v>60.97</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -3257,6 +3298,9 @@
       <c r="BK14" t="n">
         <v>65.48</v>
       </c>
+      <c r="BL14" t="n">
+        <v>65.48</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -3450,6 +3494,9 @@
       <c r="BK15" t="n">
         <v>49.59</v>
       </c>
+      <c r="BL15" t="n">
+        <v>49.59</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -3643,6 +3690,9 @@
       <c r="BK16" t="n">
         <v>47.84</v>
       </c>
+      <c r="BL16" t="n">
+        <v>47.84</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -3836,6 +3886,9 @@
       <c r="BK17" t="n">
         <v>39.83</v>
       </c>
+      <c r="BL17" t="n">
+        <v>39.83</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -4029,6 +4082,9 @@
       <c r="BK18" t="n">
         <v>42.1</v>
       </c>
+      <c r="BL18" t="n">
+        <v>42.1</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -4222,6 +4278,9 @@
       <c r="BK19" t="n">
         <v>34.94</v>
       </c>
+      <c r="BL19" t="n">
+        <v>34.94</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -4415,6 +4474,9 @@
       <c r="BK20" t="n">
         <v>38.28</v>
       </c>
+      <c r="BL20" t="n">
+        <v>38.28</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -4608,6 +4670,9 @@
       <c r="BK21" t="n">
         <v>60.32</v>
       </c>
+      <c r="BL21" t="n">
+        <v>60.32</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -4801,6 +4866,9 @@
       <c r="BK22" t="n">
         <v>66.76000000000001</v>
       </c>
+      <c r="BL22" t="n">
+        <v>66.76000000000001</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -4994,6 +5062,9 @@
       <c r="BK23" t="n">
         <v>58.78</v>
       </c>
+      <c r="BL23" t="n">
+        <v>58.78</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -5187,6 +5258,9 @@
       <c r="BK24" t="n">
         <v>58.26</v>
       </c>
+      <c r="BL24" t="n">
+        <v>58.26</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -5380,6 +5454,9 @@
       <c r="BK25" t="n">
         <v>36.32</v>
       </c>
+      <c r="BL25" t="n">
+        <v>36.32</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -5573,6 +5650,9 @@
       <c r="BK26" t="n">
         <v>46.87</v>
       </c>
+      <c r="BL26" t="n">
+        <v>46.87</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -5766,6 +5846,9 @@
       <c r="BK27" t="n">
         <v>57.11</v>
       </c>
+      <c r="BL27" t="n">
+        <v>57.11</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -5959,6 +6042,9 @@
       <c r="BK28" t="n">
         <v>40.98</v>
       </c>
+      <c r="BL28" t="n">
+        <v>40.98</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -6152,6 +6238,9 @@
       <c r="BK29" t="n">
         <v>38.55</v>
       </c>
+      <c r="BL29" t="n">
+        <v>38.55</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -6345,6 +6434,9 @@
       <c r="BK30" t="n">
         <v>59.98</v>
       </c>
+      <c r="BL30" t="n">
+        <v>59.98</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -6538,6 +6630,9 @@
       <c r="BK31" t="n">
         <v>26.93</v>
       </c>
+      <c r="BL31" t="n">
+        <v>26.93</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -6731,6 +6826,9 @@
       <c r="BK32" t="n">
         <v>53.97</v>
       </c>
+      <c r="BL32" t="n">
+        <v>53.97</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -6924,6 +7022,9 @@
       <c r="BK33" t="n">
         <v>46.27</v>
       </c>
+      <c r="BL33" t="n">
+        <v>46.27</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -7115,6 +7216,9 @@
         <v>51.36</v>
       </c>
       <c r="BK34" t="n">
+        <v>51.36</v>
+      </c>
+      <c r="BL34" t="n">
         <v>51.36</v>
       </c>
     </row>

--- a/gaa_rankings_pivot.xlsx
+++ b/gaa_rankings_pivot.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BL34"/>
+  <dimension ref="A1:BM34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -753,6 +753,11 @@
           <t>2026-08-04</t>
         </is>
       </c>
+      <c r="BM1" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -949,6 +954,9 @@
       <c r="BL2" t="n">
         <v>40.72</v>
       </c>
+      <c r="BM2" t="n">
+        <v>40.72</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1145,6 +1153,9 @@
       <c r="BL3" t="n">
         <v>61.51</v>
       </c>
+      <c r="BM3" t="n">
+        <v>61.51</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1341,6 +1352,9 @@
       <c r="BL4" t="n">
         <v>35.93</v>
       </c>
+      <c r="BM4" t="n">
+        <v>35.93</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1537,6 +1551,9 @@
       <c r="BL5" t="n">
         <v>49.37</v>
       </c>
+      <c r="BM5" t="n">
+        <v>49.37</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1733,6 +1750,9 @@
       <c r="BL6" t="n">
         <v>41.68</v>
       </c>
+      <c r="BM6" t="n">
+        <v>41.68</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1929,6 +1949,9 @@
       <c r="BL7" t="n">
         <v>60.67</v>
       </c>
+      <c r="BM7" t="n">
+        <v>60.67</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2125,6 +2148,9 @@
       <c r="BL8" t="n">
         <v>55.06</v>
       </c>
+      <c r="BM8" t="n">
+        <v>55.06</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2321,6 +2347,9 @@
       <c r="BL9" t="n">
         <v>62.59</v>
       </c>
+      <c r="BM9" t="n">
+        <v>62.59</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2517,6 +2546,9 @@
       <c r="BL10" t="n">
         <v>53.83</v>
       </c>
+      <c r="BM10" t="n">
+        <v>53.83</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2713,6 +2745,9 @@
       <c r="BL11" t="n">
         <v>60.76</v>
       </c>
+      <c r="BM11" t="n">
+        <v>60.76</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2909,6 +2944,9 @@
       <c r="BL12" t="n">
         <v>46.39</v>
       </c>
+      <c r="BM12" t="n">
+        <v>46.39</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -3105,6 +3143,9 @@
       <c r="BL13" t="n">
         <v>60.97</v>
       </c>
+      <c r="BM13" t="n">
+        <v>60.97</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -3301,6 +3342,9 @@
       <c r="BL14" t="n">
         <v>65.48</v>
       </c>
+      <c r="BM14" t="n">
+        <v>65.48</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -3497,6 +3541,9 @@
       <c r="BL15" t="n">
         <v>49.59</v>
       </c>
+      <c r="BM15" t="n">
+        <v>49.59</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -3693,6 +3740,9 @@
       <c r="BL16" t="n">
         <v>47.84</v>
       </c>
+      <c r="BM16" t="n">
+        <v>47.84</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -3889,6 +3939,9 @@
       <c r="BL17" t="n">
         <v>39.83</v>
       </c>
+      <c r="BM17" t="n">
+        <v>39.83</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -4085,6 +4138,9 @@
       <c r="BL18" t="n">
         <v>42.1</v>
       </c>
+      <c r="BM18" t="n">
+        <v>42.1</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -4281,6 +4337,9 @@
       <c r="BL19" t="n">
         <v>34.94</v>
       </c>
+      <c r="BM19" t="n">
+        <v>34.94</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -4477,6 +4536,9 @@
       <c r="BL20" t="n">
         <v>38.28</v>
       </c>
+      <c r="BM20" t="n">
+        <v>38.28</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -4673,6 +4735,9 @@
       <c r="BL21" t="n">
         <v>60.32</v>
       </c>
+      <c r="BM21" t="n">
+        <v>60.32</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -4869,6 +4934,9 @@
       <c r="BL22" t="n">
         <v>66.76000000000001</v>
       </c>
+      <c r="BM22" t="n">
+        <v>66.76000000000001</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -5065,6 +5133,9 @@
       <c r="BL23" t="n">
         <v>58.78</v>
       </c>
+      <c r="BM23" t="n">
+        <v>58.78</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -5261,6 +5332,9 @@
       <c r="BL24" t="n">
         <v>58.26</v>
       </c>
+      <c r="BM24" t="n">
+        <v>58.26</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -5457,6 +5531,9 @@
       <c r="BL25" t="n">
         <v>36.32</v>
       </c>
+      <c r="BM25" t="n">
+        <v>36.32</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -5653,6 +5730,9 @@
       <c r="BL26" t="n">
         <v>46.87</v>
       </c>
+      <c r="BM26" t="n">
+        <v>46.87</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -5849,6 +5929,9 @@
       <c r="BL27" t="n">
         <v>57.11</v>
       </c>
+      <c r="BM27" t="n">
+        <v>57.11</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -6045,6 +6128,9 @@
       <c r="BL28" t="n">
         <v>40.98</v>
       </c>
+      <c r="BM28" t="n">
+        <v>40.98</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -6241,6 +6327,9 @@
       <c r="BL29" t="n">
         <v>38.55</v>
       </c>
+      <c r="BM29" t="n">
+        <v>38.55</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -6437,6 +6526,9 @@
       <c r="BL30" t="n">
         <v>59.98</v>
       </c>
+      <c r="BM30" t="n">
+        <v>59.98</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -6633,6 +6725,9 @@
       <c r="BL31" t="n">
         <v>26.93</v>
       </c>
+      <c r="BM31" t="n">
+        <v>26.93</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -6829,6 +6924,9 @@
       <c r="BL32" t="n">
         <v>53.97</v>
       </c>
+      <c r="BM32" t="n">
+        <v>53.97</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -7025,6 +7123,9 @@
       <c r="BL33" t="n">
         <v>46.27</v>
       </c>
+      <c r="BM33" t="n">
+        <v>46.27</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -7219,6 +7320,9 @@
         <v>51.36</v>
       </c>
       <c r="BL34" t="n">
+        <v>51.36</v>
+      </c>
+      <c r="BM34" t="n">
         <v>51.36</v>
       </c>
     </row>

--- a/gaa_rankings_pivot.xlsx
+++ b/gaa_rankings_pivot.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BM34"/>
+  <dimension ref="A1:BN34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -758,6 +758,11 @@
           <t>2026-08-11</t>
         </is>
       </c>
+      <c r="BN1" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -957,6 +962,9 @@
       <c r="BM2" t="n">
         <v>40.72</v>
       </c>
+      <c r="BN2" t="n">
+        <v>40.72</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1156,6 +1164,9 @@
       <c r="BM3" t="n">
         <v>61.51</v>
       </c>
+      <c r="BN3" t="n">
+        <v>61.51</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1355,6 +1366,9 @@
       <c r="BM4" t="n">
         <v>35.93</v>
       </c>
+      <c r="BN4" t="n">
+        <v>35.93</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1554,6 +1568,9 @@
       <c r="BM5" t="n">
         <v>49.37</v>
       </c>
+      <c r="BN5" t="n">
+        <v>49.37</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1753,6 +1770,9 @@
       <c r="BM6" t="n">
         <v>41.68</v>
       </c>
+      <c r="BN6" t="n">
+        <v>41.68</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1952,6 +1972,9 @@
       <c r="BM7" t="n">
         <v>60.67</v>
       </c>
+      <c r="BN7" t="n">
+        <v>60.67</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2151,6 +2174,9 @@
       <c r="BM8" t="n">
         <v>55.06</v>
       </c>
+      <c r="BN8" t="n">
+        <v>55.06</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2350,6 +2376,9 @@
       <c r="BM9" t="n">
         <v>62.59</v>
       </c>
+      <c r="BN9" t="n">
+        <v>62.59</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2549,6 +2578,9 @@
       <c r="BM10" t="n">
         <v>53.83</v>
       </c>
+      <c r="BN10" t="n">
+        <v>53.83</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2748,6 +2780,9 @@
       <c r="BM11" t="n">
         <v>60.76</v>
       </c>
+      <c r="BN11" t="n">
+        <v>60.76</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2947,6 +2982,9 @@
       <c r="BM12" t="n">
         <v>46.39</v>
       </c>
+      <c r="BN12" t="n">
+        <v>46.39</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -3146,6 +3184,9 @@
       <c r="BM13" t="n">
         <v>60.97</v>
       </c>
+      <c r="BN13" t="n">
+        <v>60.97</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -3345,6 +3386,9 @@
       <c r="BM14" t="n">
         <v>65.48</v>
       </c>
+      <c r="BN14" t="n">
+        <v>65.48</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -3544,6 +3588,9 @@
       <c r="BM15" t="n">
         <v>49.59</v>
       </c>
+      <c r="BN15" t="n">
+        <v>49.59</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -3743,6 +3790,9 @@
       <c r="BM16" t="n">
         <v>47.84</v>
       </c>
+      <c r="BN16" t="n">
+        <v>47.84</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -3942,6 +3992,9 @@
       <c r="BM17" t="n">
         <v>39.83</v>
       </c>
+      <c r="BN17" t="n">
+        <v>39.83</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -4141,6 +4194,9 @@
       <c r="BM18" t="n">
         <v>42.1</v>
       </c>
+      <c r="BN18" t="n">
+        <v>42.1</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -4340,6 +4396,9 @@
       <c r="BM19" t="n">
         <v>34.94</v>
       </c>
+      <c r="BN19" t="n">
+        <v>34.94</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -4539,6 +4598,9 @@
       <c r="BM20" t="n">
         <v>38.28</v>
       </c>
+      <c r="BN20" t="n">
+        <v>38.28</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -4738,6 +4800,9 @@
       <c r="BM21" t="n">
         <v>60.32</v>
       </c>
+      <c r="BN21" t="n">
+        <v>60.32</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -4937,6 +5002,9 @@
       <c r="BM22" t="n">
         <v>66.76000000000001</v>
       </c>
+      <c r="BN22" t="n">
+        <v>66.76000000000001</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -5136,6 +5204,9 @@
       <c r="BM23" t="n">
         <v>58.78</v>
       </c>
+      <c r="BN23" t="n">
+        <v>58.78</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -5335,6 +5406,9 @@
       <c r="BM24" t="n">
         <v>58.26</v>
       </c>
+      <c r="BN24" t="n">
+        <v>58.26</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -5534,6 +5608,9 @@
       <c r="BM25" t="n">
         <v>36.32</v>
       </c>
+      <c r="BN25" t="n">
+        <v>36.32</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -5733,6 +5810,9 @@
       <c r="BM26" t="n">
         <v>46.87</v>
       </c>
+      <c r="BN26" t="n">
+        <v>46.87</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -5932,6 +6012,9 @@
       <c r="BM27" t="n">
         <v>57.11</v>
       </c>
+      <c r="BN27" t="n">
+        <v>57.11</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -6131,6 +6214,9 @@
       <c r="BM28" t="n">
         <v>40.98</v>
       </c>
+      <c r="BN28" t="n">
+        <v>40.98</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -6330,6 +6416,9 @@
       <c r="BM29" t="n">
         <v>38.55</v>
       </c>
+      <c r="BN29" t="n">
+        <v>38.55</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -6529,6 +6618,9 @@
       <c r="BM30" t="n">
         <v>59.98</v>
       </c>
+      <c r="BN30" t="n">
+        <v>59.98</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -6728,6 +6820,9 @@
       <c r="BM31" t="n">
         <v>26.93</v>
       </c>
+      <c r="BN31" t="n">
+        <v>26.93</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -6927,6 +7022,9 @@
       <c r="BM32" t="n">
         <v>53.97</v>
       </c>
+      <c r="BN32" t="n">
+        <v>53.97</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -7126,6 +7224,9 @@
       <c r="BM33" t="n">
         <v>46.27</v>
       </c>
+      <c r="BN33" t="n">
+        <v>46.27</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -7323,6 +7424,9 @@
         <v>51.36</v>
       </c>
       <c r="BM34" t="n">
+        <v>51.36</v>
+      </c>
+      <c r="BN34" t="n">
         <v>51.36</v>
       </c>
     </row>

--- a/gaa_rankings_pivot.xlsx
+++ b/gaa_rankings_pivot.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BN34"/>
+  <dimension ref="A1:BO34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -763,6 +763,11 @@
           <t>2026-08-18</t>
         </is>
       </c>
+      <c r="BO1" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -965,6 +970,9 @@
       <c r="BN2" t="n">
         <v>40.72</v>
       </c>
+      <c r="BO2" t="n">
+        <v>40.72</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1167,6 +1175,9 @@
       <c r="BN3" t="n">
         <v>61.51</v>
       </c>
+      <c r="BO3" t="n">
+        <v>61.51</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1369,6 +1380,9 @@
       <c r="BN4" t="n">
         <v>35.93</v>
       </c>
+      <c r="BO4" t="n">
+        <v>35.93</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1571,6 +1585,9 @@
       <c r="BN5" t="n">
         <v>49.37</v>
       </c>
+      <c r="BO5" t="n">
+        <v>49.37</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1773,6 +1790,9 @@
       <c r="BN6" t="n">
         <v>41.68</v>
       </c>
+      <c r="BO6" t="n">
+        <v>41.68</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1975,6 +1995,9 @@
       <c r="BN7" t="n">
         <v>60.67</v>
       </c>
+      <c r="BO7" t="n">
+        <v>60.67</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2177,6 +2200,9 @@
       <c r="BN8" t="n">
         <v>55.06</v>
       </c>
+      <c r="BO8" t="n">
+        <v>55.06</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2379,6 +2405,9 @@
       <c r="BN9" t="n">
         <v>62.59</v>
       </c>
+      <c r="BO9" t="n">
+        <v>62.59</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2581,6 +2610,9 @@
       <c r="BN10" t="n">
         <v>53.83</v>
       </c>
+      <c r="BO10" t="n">
+        <v>53.83</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2783,6 +2815,9 @@
       <c r="BN11" t="n">
         <v>60.76</v>
       </c>
+      <c r="BO11" t="n">
+        <v>60.76</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2985,6 +3020,9 @@
       <c r="BN12" t="n">
         <v>46.39</v>
       </c>
+      <c r="BO12" t="n">
+        <v>46.39</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -3187,6 +3225,9 @@
       <c r="BN13" t="n">
         <v>60.97</v>
       </c>
+      <c r="BO13" t="n">
+        <v>60.97</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -3389,6 +3430,9 @@
       <c r="BN14" t="n">
         <v>65.48</v>
       </c>
+      <c r="BO14" t="n">
+        <v>65.48</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -3591,6 +3635,9 @@
       <c r="BN15" t="n">
         <v>49.59</v>
       </c>
+      <c r="BO15" t="n">
+        <v>49.59</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -3793,6 +3840,9 @@
       <c r="BN16" t="n">
         <v>47.84</v>
       </c>
+      <c r="BO16" t="n">
+        <v>47.84</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -3995,6 +4045,9 @@
       <c r="BN17" t="n">
         <v>39.83</v>
       </c>
+      <c r="BO17" t="n">
+        <v>39.83</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -4197,6 +4250,9 @@
       <c r="BN18" t="n">
         <v>42.1</v>
       </c>
+      <c r="BO18" t="n">
+        <v>42.1</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -4399,6 +4455,9 @@
       <c r="BN19" t="n">
         <v>34.94</v>
       </c>
+      <c r="BO19" t="n">
+        <v>34.94</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -4601,6 +4660,9 @@
       <c r="BN20" t="n">
         <v>38.28</v>
       </c>
+      <c r="BO20" t="n">
+        <v>38.28</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -4803,6 +4865,9 @@
       <c r="BN21" t="n">
         <v>60.32</v>
       </c>
+      <c r="BO21" t="n">
+        <v>60.32</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -5005,6 +5070,9 @@
       <c r="BN22" t="n">
         <v>66.76000000000001</v>
       </c>
+      <c r="BO22" t="n">
+        <v>66.76000000000001</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -5207,6 +5275,9 @@
       <c r="BN23" t="n">
         <v>58.78</v>
       </c>
+      <c r="BO23" t="n">
+        <v>58.78</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -5409,6 +5480,9 @@
       <c r="BN24" t="n">
         <v>58.26</v>
       </c>
+      <c r="BO24" t="n">
+        <v>58.26</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -5611,6 +5685,9 @@
       <c r="BN25" t="n">
         <v>36.32</v>
       </c>
+      <c r="BO25" t="n">
+        <v>36.32</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -5813,6 +5890,9 @@
       <c r="BN26" t="n">
         <v>46.87</v>
       </c>
+      <c r="BO26" t="n">
+        <v>46.87</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -6015,6 +6095,9 @@
       <c r="BN27" t="n">
         <v>57.11</v>
       </c>
+      <c r="BO27" t="n">
+        <v>57.11</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -6217,6 +6300,9 @@
       <c r="BN28" t="n">
         <v>40.98</v>
       </c>
+      <c r="BO28" t="n">
+        <v>40.98</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -6419,6 +6505,9 @@
       <c r="BN29" t="n">
         <v>38.55</v>
       </c>
+      <c r="BO29" t="n">
+        <v>38.55</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -6621,6 +6710,9 @@
       <c r="BN30" t="n">
         <v>59.98</v>
       </c>
+      <c r="BO30" t="n">
+        <v>59.98</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -6823,6 +6915,9 @@
       <c r="BN31" t="n">
         <v>26.93</v>
       </c>
+      <c r="BO31" t="n">
+        <v>26.93</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -7025,6 +7120,9 @@
       <c r="BN32" t="n">
         <v>53.97</v>
       </c>
+      <c r="BO32" t="n">
+        <v>53.97</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -7227,6 +7325,9 @@
       <c r="BN33" t="n">
         <v>46.27</v>
       </c>
+      <c r="BO33" t="n">
+        <v>46.27</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -7427,6 +7528,9 @@
         <v>51.36</v>
       </c>
       <c r="BN34" t="n">
+        <v>51.36</v>
+      </c>
+      <c r="BO34" t="n">
         <v>51.36</v>
       </c>
     </row>

--- a/gaa_rankings_pivot.xlsx
+++ b/gaa_rankings_pivot.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BO34"/>
+  <dimension ref="A1:BP34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -768,6 +768,11 @@
           <t>2026-08-25</t>
         </is>
       </c>
+      <c r="BP1" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -973,6 +978,9 @@
       <c r="BO2" t="n">
         <v>40.72</v>
       </c>
+      <c r="BP2" t="n">
+        <v>40.72</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1178,6 +1186,9 @@
       <c r="BO3" t="n">
         <v>61.51</v>
       </c>
+      <c r="BP3" t="n">
+        <v>61.51</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1383,6 +1394,9 @@
       <c r="BO4" t="n">
         <v>35.93</v>
       </c>
+      <c r="BP4" t="n">
+        <v>35.93</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1588,6 +1602,9 @@
       <c r="BO5" t="n">
         <v>49.37</v>
       </c>
+      <c r="BP5" t="n">
+        <v>49.37</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1793,6 +1810,9 @@
       <c r="BO6" t="n">
         <v>41.68</v>
       </c>
+      <c r="BP6" t="n">
+        <v>41.68</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1998,6 +2018,9 @@
       <c r="BO7" t="n">
         <v>60.67</v>
       </c>
+      <c r="BP7" t="n">
+        <v>60.67</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2203,6 +2226,9 @@
       <c r="BO8" t="n">
         <v>55.06</v>
       </c>
+      <c r="BP8" t="n">
+        <v>55.06</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2408,6 +2434,9 @@
       <c r="BO9" t="n">
         <v>62.59</v>
       </c>
+      <c r="BP9" t="n">
+        <v>62.59</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2613,6 +2642,9 @@
       <c r="BO10" t="n">
         <v>53.83</v>
       </c>
+      <c r="BP10" t="n">
+        <v>53.83</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2818,6 +2850,9 @@
       <c r="BO11" t="n">
         <v>60.76</v>
       </c>
+      <c r="BP11" t="n">
+        <v>60.76</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -3023,6 +3058,9 @@
       <c r="BO12" t="n">
         <v>46.39</v>
       </c>
+      <c r="BP12" t="n">
+        <v>46.39</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -3228,6 +3266,9 @@
       <c r="BO13" t="n">
         <v>60.97</v>
       </c>
+      <c r="BP13" t="n">
+        <v>60.97</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -3433,6 +3474,9 @@
       <c r="BO14" t="n">
         <v>65.48</v>
       </c>
+      <c r="BP14" t="n">
+        <v>65.48</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -3638,6 +3682,9 @@
       <c r="BO15" t="n">
         <v>49.59</v>
       </c>
+      <c r="BP15" t="n">
+        <v>49.59</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -3843,6 +3890,9 @@
       <c r="BO16" t="n">
         <v>47.84</v>
       </c>
+      <c r="BP16" t="n">
+        <v>47.84</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -4048,6 +4098,9 @@
       <c r="BO17" t="n">
         <v>39.83</v>
       </c>
+      <c r="BP17" t="n">
+        <v>39.83</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -4253,6 +4306,9 @@
       <c r="BO18" t="n">
         <v>42.1</v>
       </c>
+      <c r="BP18" t="n">
+        <v>42.1</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -4458,6 +4514,9 @@
       <c r="BO19" t="n">
         <v>34.94</v>
       </c>
+      <c r="BP19" t="n">
+        <v>34.94</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -4663,6 +4722,9 @@
       <c r="BO20" t="n">
         <v>38.28</v>
       </c>
+      <c r="BP20" t="n">
+        <v>38.28</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -4868,6 +4930,9 @@
       <c r="BO21" t="n">
         <v>60.32</v>
       </c>
+      <c r="BP21" t="n">
+        <v>60.32</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -5073,6 +5138,9 @@
       <c r="BO22" t="n">
         <v>66.76000000000001</v>
       </c>
+      <c r="BP22" t="n">
+        <v>66.76000000000001</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -5278,6 +5346,9 @@
       <c r="BO23" t="n">
         <v>58.78</v>
       </c>
+      <c r="BP23" t="n">
+        <v>58.78</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -5483,6 +5554,9 @@
       <c r="BO24" t="n">
         <v>58.26</v>
       </c>
+      <c r="BP24" t="n">
+        <v>58.26</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -5688,6 +5762,9 @@
       <c r="BO25" t="n">
         <v>36.32</v>
       </c>
+      <c r="BP25" t="n">
+        <v>36.32</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -5893,6 +5970,9 @@
       <c r="BO26" t="n">
         <v>46.87</v>
       </c>
+      <c r="BP26" t="n">
+        <v>46.87</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -6098,6 +6178,9 @@
       <c r="BO27" t="n">
         <v>57.11</v>
       </c>
+      <c r="BP27" t="n">
+        <v>57.11</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -6303,6 +6386,9 @@
       <c r="BO28" t="n">
         <v>40.98</v>
       </c>
+      <c r="BP28" t="n">
+        <v>40.98</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -6508,6 +6594,9 @@
       <c r="BO29" t="n">
         <v>38.55</v>
       </c>
+      <c r="BP29" t="n">
+        <v>38.55</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -6713,6 +6802,9 @@
       <c r="BO30" t="n">
         <v>59.98</v>
       </c>
+      <c r="BP30" t="n">
+        <v>59.98</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -6918,6 +7010,9 @@
       <c r="BO31" t="n">
         <v>26.93</v>
       </c>
+      <c r="BP31" t="n">
+        <v>26.93</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -7123,6 +7218,9 @@
       <c r="BO32" t="n">
         <v>53.97</v>
       </c>
+      <c r="BP32" t="n">
+        <v>53.97</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -7328,6 +7426,9 @@
       <c r="BO33" t="n">
         <v>46.27</v>
       </c>
+      <c r="BP33" t="n">
+        <v>46.27</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -7531,6 +7632,9 @@
         <v>51.36</v>
       </c>
       <c r="BO34" t="n">
+        <v>51.36</v>
+      </c>
+      <c r="BP34" t="n">
         <v>51.36</v>
       </c>
     </row>

--- a/gaa_rankings_pivot.xlsx
+++ b/gaa_rankings_pivot.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP34"/>
+  <dimension ref="A1:BQ34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -773,6 +773,11 @@
           <t>2026-09-01</t>
         </is>
       </c>
+      <c r="BQ1" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -981,6 +986,9 @@
       <c r="BP2" t="n">
         <v>40.72</v>
       </c>
+      <c r="BQ2" t="n">
+        <v>40.72</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1189,6 +1197,9 @@
       <c r="BP3" t="n">
         <v>61.51</v>
       </c>
+      <c r="BQ3" t="n">
+        <v>61.51</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1397,6 +1408,9 @@
       <c r="BP4" t="n">
         <v>35.93</v>
       </c>
+      <c r="BQ4" t="n">
+        <v>35.93</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1605,6 +1619,9 @@
       <c r="BP5" t="n">
         <v>49.37</v>
       </c>
+      <c r="BQ5" t="n">
+        <v>49.37</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1813,6 +1830,9 @@
       <c r="BP6" t="n">
         <v>41.68</v>
       </c>
+      <c r="BQ6" t="n">
+        <v>41.68</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2021,6 +2041,9 @@
       <c r="BP7" t="n">
         <v>60.67</v>
       </c>
+      <c r="BQ7" t="n">
+        <v>60.67</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2229,6 +2252,9 @@
       <c r="BP8" t="n">
         <v>55.06</v>
       </c>
+      <c r="BQ8" t="n">
+        <v>55.06</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2437,6 +2463,9 @@
       <c r="BP9" t="n">
         <v>62.59</v>
       </c>
+      <c r="BQ9" t="n">
+        <v>62.59</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2645,6 +2674,9 @@
       <c r="BP10" t="n">
         <v>53.83</v>
       </c>
+      <c r="BQ10" t="n">
+        <v>53.83</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2853,6 +2885,9 @@
       <c r="BP11" t="n">
         <v>60.76</v>
       </c>
+      <c r="BQ11" t="n">
+        <v>60.76</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -3061,6 +3096,9 @@
       <c r="BP12" t="n">
         <v>46.39</v>
       </c>
+      <c r="BQ12" t="n">
+        <v>46.39</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -3269,6 +3307,9 @@
       <c r="BP13" t="n">
         <v>60.97</v>
       </c>
+      <c r="BQ13" t="n">
+        <v>60.97</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -3477,6 +3518,9 @@
       <c r="BP14" t="n">
         <v>65.48</v>
       </c>
+      <c r="BQ14" t="n">
+        <v>65.48</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -3685,6 +3729,9 @@
       <c r="BP15" t="n">
         <v>49.59</v>
       </c>
+      <c r="BQ15" t="n">
+        <v>49.59</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -3893,6 +3940,9 @@
       <c r="BP16" t="n">
         <v>47.84</v>
       </c>
+      <c r="BQ16" t="n">
+        <v>47.84</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -4101,6 +4151,9 @@
       <c r="BP17" t="n">
         <v>39.83</v>
       </c>
+      <c r="BQ17" t="n">
+        <v>39.83</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -4309,6 +4362,9 @@
       <c r="BP18" t="n">
         <v>42.1</v>
       </c>
+      <c r="BQ18" t="n">
+        <v>42.1</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -4517,6 +4573,9 @@
       <c r="BP19" t="n">
         <v>34.94</v>
       </c>
+      <c r="BQ19" t="n">
+        <v>34.94</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -4725,6 +4784,9 @@
       <c r="BP20" t="n">
         <v>38.28</v>
       </c>
+      <c r="BQ20" t="n">
+        <v>38.28</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -4933,6 +4995,9 @@
       <c r="BP21" t="n">
         <v>60.32</v>
       </c>
+      <c r="BQ21" t="n">
+        <v>60.32</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -5141,6 +5206,9 @@
       <c r="BP22" t="n">
         <v>66.76000000000001</v>
       </c>
+      <c r="BQ22" t="n">
+        <v>66.76000000000001</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -5349,6 +5417,9 @@
       <c r="BP23" t="n">
         <v>58.78</v>
       </c>
+      <c r="BQ23" t="n">
+        <v>58.78</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -5557,6 +5628,9 @@
       <c r="BP24" t="n">
         <v>58.26</v>
       </c>
+      <c r="BQ24" t="n">
+        <v>58.26</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -5765,6 +5839,9 @@
       <c r="BP25" t="n">
         <v>36.32</v>
       </c>
+      <c r="BQ25" t="n">
+        <v>36.32</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -5973,6 +6050,9 @@
       <c r="BP26" t="n">
         <v>46.87</v>
       </c>
+      <c r="BQ26" t="n">
+        <v>46.87</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -6181,6 +6261,9 @@
       <c r="BP27" t="n">
         <v>57.11</v>
       </c>
+      <c r="BQ27" t="n">
+        <v>57.11</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -6389,6 +6472,9 @@
       <c r="BP28" t="n">
         <v>40.98</v>
       </c>
+      <c r="BQ28" t="n">
+        <v>40.98</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -6597,6 +6683,9 @@
       <c r="BP29" t="n">
         <v>38.55</v>
       </c>
+      <c r="BQ29" t="n">
+        <v>38.55</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -6805,6 +6894,9 @@
       <c r="BP30" t="n">
         <v>59.98</v>
       </c>
+      <c r="BQ30" t="n">
+        <v>59.98</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -7013,6 +7105,9 @@
       <c r="BP31" t="n">
         <v>26.93</v>
       </c>
+      <c r="BQ31" t="n">
+        <v>26.93</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -7221,6 +7316,9 @@
       <c r="BP32" t="n">
         <v>53.97</v>
       </c>
+      <c r="BQ32" t="n">
+        <v>53.97</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -7429,6 +7527,9 @@
       <c r="BP33" t="n">
         <v>46.27</v>
       </c>
+      <c r="BQ33" t="n">
+        <v>46.27</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -7635,6 +7736,9 @@
         <v>51.36</v>
       </c>
       <c r="BP34" t="n">
+        <v>51.36</v>
+      </c>
+      <c r="BQ34" t="n">
         <v>51.36</v>
       </c>
     </row>
